--- a/reports/Selenium_Web_Test_Report.xlsx
+++ b/reports/Selenium_Web_Test_Report.xlsx
@@ -6384,7 +6384,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>2026-06-13 13:17:45</t>
+          <t>2026-06-14 21:34:59</t>
         </is>
       </c>
     </row>

--- a/reports/Selenium_Web_Test_Report.xlsx
+++ b/reports/Selenium_Web_Test_Report.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,6 +38,10 @@
     <font>
       <b val="1"/>
       <color rgb="00008000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF0000"/>
     </font>
     <font>
       <b val="1"/>
@@ -75,7 +79,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -92,7 +96,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -459,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G191"/>
+  <dimension ref="A1:G361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -542,7 +549,7 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>653</v>
+        <v>360</v>
       </c>
       <c r="G4" s="4" t="inlineStr"/>
     </row>
@@ -573,7 +580,7 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>67</v>
+        <v>199</v>
       </c>
       <c r="G5" s="4" t="inlineStr"/>
     </row>
@@ -604,7 +611,7 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>62</v>
+        <v>122</v>
       </c>
       <c r="G6" s="4" t="inlineStr"/>
     </row>
@@ -635,7 +642,7 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>53</v>
+        <v>196</v>
       </c>
       <c r="G7" s="4" t="inlineStr"/>
     </row>
@@ -666,7 +673,7 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="G8" s="4" t="inlineStr"/>
     </row>
@@ -697,7 +704,7 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4076</v>
+        <v>4103</v>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
     </row>
@@ -728,7 +735,7 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>48</v>
+        <v>85</v>
       </c>
       <c r="G10" s="4" t="inlineStr"/>
     </row>
@@ -759,7 +766,7 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>42</v>
+        <v>153</v>
       </c>
       <c r="G11" s="4" t="inlineStr"/>
     </row>
@@ -790,7 +797,7 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>2099</v>
+        <v>2214</v>
       </c>
       <c r="G12" s="4" t="inlineStr"/>
     </row>
@@ -821,7 +828,7 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>2133</v>
+        <v>2335</v>
       </c>
       <c r="G13" s="4" t="inlineStr"/>
     </row>
@@ -852,7 +859,7 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>60</v>
+        <v>189</v>
       </c>
       <c r="G14" s="4" t="inlineStr"/>
     </row>
@@ -883,7 +890,7 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>68</v>
+        <v>190</v>
       </c>
       <c r="G15" s="4" t="inlineStr"/>
     </row>
@@ -914,7 +921,7 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>546</v>
+        <v>856</v>
       </c>
       <c r="G16" s="4" t="inlineStr"/>
     </row>
@@ -945,7 +952,7 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>128</v>
+        <v>317</v>
       </c>
       <c r="G17" s="4" t="inlineStr"/>
     </row>
@@ -976,7 +983,7 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>101</v>
+        <v>473</v>
       </c>
       <c r="G18" s="4" t="inlineStr"/>
     </row>
@@ -1007,7 +1014,7 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>80</v>
+        <v>238</v>
       </c>
       <c r="G19" s="4" t="inlineStr"/>
     </row>
@@ -1038,7 +1045,7 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>89</v>
+        <v>187</v>
       </c>
       <c r="G20" s="4" t="inlineStr"/>
     </row>
@@ -1069,7 +1076,7 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>117</v>
+        <v>246</v>
       </c>
       <c r="G21" s="4" t="inlineStr"/>
     </row>
@@ -1100,7 +1107,7 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2374</v>
+        <v>2440</v>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
     </row>
@@ -1131,7 +1138,7 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>2418</v>
+        <v>2768</v>
       </c>
       <c r="G23" s="4" t="inlineStr"/>
     </row>
@@ -1162,7 +1169,7 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>8564</v>
+        <v>9079</v>
       </c>
       <c r="G24" s="4" t="inlineStr"/>
     </row>
@@ -1193,7 +1200,7 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>8649</v>
+        <v>9018</v>
       </c>
       <c r="G25" s="4" t="inlineStr"/>
     </row>
@@ -1224,7 +1231,7 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>8640</v>
+        <v>9144</v>
       </c>
       <c r="G26" s="4" t="inlineStr"/>
     </row>
@@ -1255,7 +1262,7 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>8493</v>
+        <v>8834</v>
       </c>
       <c r="G27" s="4" t="inlineStr"/>
     </row>
@@ -1286,7 +1293,7 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2114</v>
+        <v>2212</v>
       </c>
       <c r="G28" s="4" t="inlineStr"/>
     </row>
@@ -1317,7 +1324,7 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>2086</v>
+        <v>2132</v>
       </c>
       <c r="G29" s="4" t="inlineStr"/>
     </row>
@@ -1348,7 +1355,7 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>2054</v>
+        <v>2144</v>
       </c>
       <c r="G30" s="4" t="inlineStr"/>
     </row>
@@ -1379,7 +1386,7 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>572</v>
+        <v>407</v>
       </c>
       <c r="G31" s="4" t="inlineStr"/>
     </row>
@@ -1410,7 +1417,7 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>58</v>
+        <v>118</v>
       </c>
       <c r="G32" s="4" t="inlineStr"/>
     </row>
@@ -1441,7 +1448,7 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="G33" s="4" t="inlineStr"/>
     </row>
@@ -1472,7 +1479,7 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>2305</v>
+        <v>2196</v>
       </c>
       <c r="G34" s="4" t="inlineStr"/>
     </row>
@@ -1503,7 +1510,7 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>8491</v>
+        <v>8550</v>
       </c>
       <c r="G35" s="4" t="inlineStr"/>
     </row>
@@ -1534,7 +1541,7 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>10309</v>
+        <v>10600</v>
       </c>
       <c r="G36" s="4" t="inlineStr"/>
     </row>
@@ -1565,7 +1572,7 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>10467</v>
+        <v>10745</v>
       </c>
       <c r="G37" s="4" t="inlineStr"/>
     </row>
@@ -1596,7 +1603,7 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>10508</v>
+        <v>10916</v>
       </c>
       <c r="G38" s="4" t="inlineStr"/>
     </row>
@@ -1627,7 +1634,7 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>10524</v>
+        <v>10757</v>
       </c>
       <c r="G39" s="4" t="inlineStr"/>
     </row>
@@ -1658,7 +1665,7 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>10301</v>
+        <v>10615</v>
       </c>
       <c r="G40" s="4" t="inlineStr"/>
     </row>
@@ -1689,7 +1696,7 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>12519</v>
+        <v>12911</v>
       </c>
       <c r="G41" s="4" t="inlineStr"/>
     </row>
@@ -1720,7 +1727,7 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>4061</v>
+        <v>4065</v>
       </c>
       <c r="G42" s="4" t="inlineStr"/>
     </row>
@@ -1751,7 +1758,7 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>2136</v>
+        <v>2275</v>
       </c>
       <c r="G43" s="4" t="inlineStr"/>
     </row>
@@ -1782,7 +1789,7 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="G44" s="4" t="inlineStr"/>
     </row>
@@ -1813,7 +1820,7 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="G45" s="4" t="inlineStr"/>
     </row>
@@ -1844,7 +1851,7 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>4057</v>
+        <v>4129</v>
       </c>
       <c r="G46" s="4" t="inlineStr"/>
     </row>
@@ -1875,7 +1882,7 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>4069</v>
+        <v>4119</v>
       </c>
       <c r="G47" s="4" t="inlineStr"/>
     </row>
@@ -1906,7 +1913,7 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>8121</v>
+        <v>8273</v>
       </c>
       <c r="G48" s="4" t="inlineStr"/>
     </row>
@@ -1937,7 +1944,7 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>4095</v>
+        <v>4286</v>
       </c>
       <c r="G49" s="4" t="inlineStr"/>
     </row>
@@ -1968,7 +1975,7 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>4129</v>
+        <v>4219</v>
       </c>
       <c r="G50" s="4" t="inlineStr"/>
     </row>
@@ -1999,7 +2006,7 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>4132</v>
+        <v>4158</v>
       </c>
       <c r="G51" s="4" t="inlineStr"/>
     </row>
@@ -2030,7 +2037,7 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>10124</v>
+        <v>10240</v>
       </c>
       <c r="G52" s="4" t="inlineStr"/>
     </row>
@@ -2061,7 +2068,7 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>6178</v>
+        <v>6387</v>
       </c>
       <c r="G53" s="4" t="inlineStr"/>
     </row>
@@ -2092,7 +2099,7 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>12464</v>
+        <v>13019</v>
       </c>
       <c r="G54" s="4" t="inlineStr"/>
     </row>
@@ -2123,7 +2130,7 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>4050</v>
+        <v>4135</v>
       </c>
       <c r="G55" s="4" t="inlineStr"/>
     </row>
@@ -2154,7 +2161,7 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>4056</v>
+        <v>4062</v>
       </c>
       <c r="G56" s="4" t="inlineStr"/>
     </row>
@@ -2185,7 +2192,7 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>4159</v>
+        <v>4355</v>
       </c>
       <c r="G57" s="4" t="inlineStr"/>
     </row>
@@ -2216,7 +2223,7 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>4163</v>
+        <v>4318</v>
       </c>
       <c r="G58" s="4" t="inlineStr"/>
     </row>
@@ -2247,7 +2254,7 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>4180</v>
+        <v>4312</v>
       </c>
       <c r="G59" s="4" t="inlineStr"/>
     </row>
@@ -2278,7 +2285,7 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>11230</v>
+        <v>11363</v>
       </c>
       <c r="G60" s="4" t="inlineStr"/>
     </row>
@@ -2309,7 +2316,7 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>4067</v>
+        <v>4048</v>
       </c>
       <c r="G61" s="4" t="inlineStr"/>
     </row>
@@ -2340,7 +2347,7 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>4046</v>
+        <v>4085</v>
       </c>
       <c r="G62" s="4" t="inlineStr"/>
     </row>
@@ -2371,7 +2378,7 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>4027</v>
+        <v>4100</v>
       </c>
       <c r="G63" s="4" t="inlineStr"/>
     </row>
@@ -2402,7 +2409,7 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>15064</v>
+        <v>15116</v>
       </c>
       <c r="G64" s="4" t="inlineStr"/>
     </row>
@@ -2433,7 +2440,7 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>62</v>
+        <v>192</v>
       </c>
       <c r="G65" s="4" t="inlineStr"/>
     </row>
@@ -2464,7 +2471,7 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>4064</v>
+        <v>4074</v>
       </c>
       <c r="G66" s="4" t="inlineStr"/>
     </row>
@@ -2495,7 +2502,7 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>8031</v>
+        <v>8066</v>
       </c>
       <c r="G67" s="4" t="inlineStr"/>
     </row>
@@ -2526,7 +2533,7 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>4044</v>
+        <v>4114</v>
       </c>
       <c r="G68" s="4" t="inlineStr"/>
     </row>
@@ -2557,7 +2564,7 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>4053</v>
+        <v>4052</v>
       </c>
       <c r="G69" s="4" t="inlineStr"/>
     </row>
@@ -2588,7 +2595,7 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>4060</v>
+        <v>4050</v>
       </c>
       <c r="G70" s="4" t="inlineStr"/>
     </row>
@@ -2619,7 +2626,7 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>8048</v>
+        <v>8140</v>
       </c>
       <c r="G71" s="4" t="inlineStr"/>
     </row>
@@ -2650,7 +2657,7 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>16119</v>
+        <v>16261</v>
       </c>
       <c r="G72" s="4" t="inlineStr"/>
     </row>
@@ -2681,7 +2688,7 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>8033</v>
+        <v>8174</v>
       </c>
       <c r="G73" s="4" t="inlineStr"/>
     </row>
@@ -2712,7 +2719,7 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>9690</v>
+        <v>10267</v>
       </c>
       <c r="G74" s="4" t="inlineStr"/>
     </row>
@@ -2743,7 +2750,7 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>6177</v>
+        <v>6144</v>
       </c>
       <c r="G75" s="4" t="inlineStr"/>
     </row>
@@ -2805,7 +2812,7 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>4146</v>
+        <v>4101</v>
       </c>
       <c r="G77" s="4" t="inlineStr"/>
     </row>
@@ -2836,7 +2843,7 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>8189</v>
+        <v>8063</v>
       </c>
       <c r="G78" s="4" t="inlineStr"/>
     </row>
@@ -2867,7 +2874,7 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>4196</v>
+        <v>4076</v>
       </c>
       <c r="G79" s="4" t="inlineStr"/>
     </row>
@@ -2898,7 +2905,7 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="G80" s="4" t="inlineStr"/>
     </row>
@@ -2929,7 +2936,7 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>4179</v>
+        <v>4055</v>
       </c>
       <c r="G81" s="4" t="inlineStr"/>
     </row>
@@ -2960,7 +2967,7 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>4148</v>
+        <v>4126</v>
       </c>
       <c r="G82" s="4" t="inlineStr"/>
     </row>
@@ -2991,7 +2998,7 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>4133</v>
+        <v>4122</v>
       </c>
       <c r="G83" s="4" t="inlineStr"/>
     </row>
@@ -3053,7 +3060,7 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>16222</v>
+        <v>16259</v>
       </c>
       <c r="G85" s="4" t="inlineStr"/>
     </row>
@@ -3084,7 +3091,7 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>8178</v>
+        <v>8144</v>
       </c>
       <c r="G86" s="4" t="inlineStr"/>
     </row>
@@ -3115,7 +3122,7 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>8153</v>
+        <v>8151</v>
       </c>
       <c r="G87" s="4" t="inlineStr"/>
     </row>
@@ -3146,7 +3153,7 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>4132</v>
+        <v>4129</v>
       </c>
       <c r="G88" s="4" t="inlineStr"/>
     </row>
@@ -3177,7 +3184,7 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>8139</v>
+        <v>8131</v>
       </c>
       <c r="G89" s="4" t="inlineStr"/>
     </row>
@@ -3208,7 +3215,7 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>6061</v>
+        <v>6113</v>
       </c>
       <c r="G90" s="4" t="inlineStr"/>
     </row>
@@ -3239,7 +3246,7 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>4186</v>
+        <v>4183</v>
       </c>
       <c r="G91" s="4" t="inlineStr"/>
     </row>
@@ -3301,7 +3308,7 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>4153</v>
+        <v>4121</v>
       </c>
       <c r="G93" s="4" t="inlineStr"/>
     </row>
@@ -3332,7 +3339,7 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>4165</v>
+        <v>4153</v>
       </c>
       <c r="G94" s="4" t="inlineStr"/>
     </row>
@@ -3363,7 +3370,7 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>3206</v>
+        <v>2941</v>
       </c>
       <c r="G95" s="4" t="inlineStr"/>
     </row>
@@ -3394,7 +3401,7 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>2567</v>
+        <v>2425</v>
       </c>
       <c r="G96" s="4" t="inlineStr"/>
     </row>
@@ -3425,7 +3432,7 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>2777</v>
+        <v>2551</v>
       </c>
       <c r="G97" s="4" t="inlineStr"/>
     </row>
@@ -3456,7 +3463,7 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>2286</v>
+        <v>2220</v>
       </c>
       <c r="G98" s="4" t="inlineStr"/>
     </row>
@@ -3487,7 +3494,7 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>2749</v>
+        <v>2477</v>
       </c>
       <c r="G99" s="4" t="inlineStr"/>
     </row>
@@ -3518,7 +3525,7 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>15264</v>
+        <v>15130</v>
       </c>
       <c r="G100" s="4" t="inlineStr"/>
     </row>
@@ -3549,7 +3556,7 @@
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>6249</v>
+        <v>6491</v>
       </c>
       <c r="G101" s="4" t="inlineStr"/>
     </row>
@@ -3580,7 +3587,7 @@
         </is>
       </c>
       <c r="F102" s="3" t="n">
-        <v>6282</v>
+        <v>6756</v>
       </c>
       <c r="G102" s="4" t="inlineStr"/>
     </row>
@@ -3611,7 +3618,7 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>6233</v>
+        <v>6325</v>
       </c>
       <c r="G103" s="4" t="inlineStr"/>
     </row>
@@ -3642,7 +3649,7 @@
         </is>
       </c>
       <c r="F104" s="3" t="n">
-        <v>96</v>
+        <v>224</v>
       </c>
       <c r="G104" s="4" t="inlineStr"/>
     </row>
@@ -3673,7 +3680,7 @@
         </is>
       </c>
       <c r="F105" s="3" t="n">
-        <v>2361</v>
+        <v>2536</v>
       </c>
       <c r="G105" s="4" t="inlineStr"/>
     </row>
@@ -3704,7 +3711,7 @@
         </is>
       </c>
       <c r="F106" s="3" t="n">
-        <v>8266</v>
+        <v>8573</v>
       </c>
       <c r="G106" s="4" t="inlineStr"/>
     </row>
@@ -3735,7 +3742,7 @@
         </is>
       </c>
       <c r="F107" s="3" t="n">
-        <v>4756</v>
+        <v>4520</v>
       </c>
       <c r="G107" s="4" t="inlineStr"/>
     </row>
@@ -3766,7 +3773,7 @@
         </is>
       </c>
       <c r="F108" s="3" t="n">
-        <v>4123</v>
+        <v>4229</v>
       </c>
       <c r="G108" s="4" t="inlineStr"/>
     </row>
@@ -3797,7 +3804,7 @@
         </is>
       </c>
       <c r="F109" s="3" t="n">
-        <v>4098</v>
+        <v>4204</v>
       </c>
       <c r="G109" s="4" t="inlineStr"/>
     </row>
@@ -3828,7 +3835,7 @@
         </is>
       </c>
       <c r="F110" s="3" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G110" s="4" t="inlineStr"/>
     </row>
@@ -3859,7 +3866,7 @@
         </is>
       </c>
       <c r="F111" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G111" s="4" t="inlineStr"/>
     </row>
@@ -3890,7 +3897,7 @@
         </is>
       </c>
       <c r="F112" s="3" t="n">
-        <v>188</v>
+        <v>359</v>
       </c>
       <c r="G112" s="4" t="inlineStr"/>
     </row>
@@ -3921,7 +3928,7 @@
         </is>
       </c>
       <c r="F113" s="3" t="n">
-        <v>186</v>
+        <v>353</v>
       </c>
       <c r="G113" s="4" t="inlineStr"/>
     </row>
@@ -3952,7 +3959,7 @@
         </is>
       </c>
       <c r="F114" s="3" t="n">
-        <v>188</v>
+        <v>349</v>
       </c>
       <c r="G114" s="4" t="inlineStr"/>
     </row>
@@ -3983,7 +3990,7 @@
         </is>
       </c>
       <c r="F115" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G115" s="4" t="inlineStr"/>
     </row>
@@ -4014,7 +4021,7 @@
         </is>
       </c>
       <c r="F116" s="3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G116" s="4" t="inlineStr"/>
     </row>
@@ -4045,7 +4052,7 @@
         </is>
       </c>
       <c r="F117" s="3" t="n">
-        <v>4481</v>
+        <v>4425</v>
       </c>
       <c r="G117" s="4" t="inlineStr"/>
     </row>
@@ -4076,7 +4083,7 @@
         </is>
       </c>
       <c r="F118" s="3" t="n">
-        <v>4124</v>
+        <v>4180</v>
       </c>
       <c r="G118" s="4" t="inlineStr"/>
     </row>
@@ -4107,7 +4114,7 @@
         </is>
       </c>
       <c r="F119" s="3" t="n">
-        <v>4084</v>
+        <v>4185</v>
       </c>
       <c r="G119" s="4" t="inlineStr"/>
     </row>
@@ -4138,7 +4145,7 @@
         </is>
       </c>
       <c r="F120" s="3" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="G120" s="4" t="inlineStr"/>
     </row>
@@ -4169,7 +4176,7 @@
         </is>
       </c>
       <c r="F121" s="3" t="n">
-        <v>4064</v>
+        <v>4080</v>
       </c>
       <c r="G121" s="4" t="inlineStr"/>
     </row>
@@ -4200,7 +4207,7 @@
         </is>
       </c>
       <c r="F122" s="3" t="n">
-        <v>4082</v>
+        <v>4102</v>
       </c>
       <c r="G122" s="4" t="inlineStr"/>
     </row>
@@ -4231,7 +4238,7 @@
         </is>
       </c>
       <c r="F123" s="3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G123" s="4" t="inlineStr"/>
     </row>
@@ -4262,7 +4269,7 @@
         </is>
       </c>
       <c r="F124" s="3" t="n">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="G124" s="4" t="inlineStr"/>
     </row>
@@ -4293,7 +4300,7 @@
         </is>
       </c>
       <c r="F125" s="3" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G125" s="4" t="inlineStr"/>
     </row>
@@ -4324,7 +4331,7 @@
         </is>
       </c>
       <c r="F126" s="3" t="n">
-        <v>6513</v>
+        <v>6375</v>
       </c>
       <c r="G126" s="4" t="inlineStr"/>
     </row>
@@ -4355,7 +4362,7 @@
         </is>
       </c>
       <c r="F127" s="3" t="n">
-        <v>2773</v>
+        <v>2037</v>
       </c>
       <c r="G127" s="4" t="inlineStr"/>
     </row>
@@ -4386,7 +4393,7 @@
         </is>
       </c>
       <c r="F128" s="3" t="n">
-        <v>2156</v>
+        <v>2147</v>
       </c>
       <c r="G128" s="4" t="inlineStr"/>
     </row>
@@ -4448,7 +4455,7 @@
         </is>
       </c>
       <c r="F130" s="3" t="n">
-        <v>499</v>
+        <v>366</v>
       </c>
       <c r="G130" s="4" t="inlineStr"/>
     </row>
@@ -4479,7 +4486,7 @@
         </is>
       </c>
       <c r="F131" s="3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G131" s="4" t="inlineStr"/>
     </row>
@@ -4510,7 +4517,7 @@
         </is>
       </c>
       <c r="F132" s="3" t="n">
-        <v>462</v>
+        <v>379</v>
       </c>
       <c r="G132" s="4" t="inlineStr"/>
     </row>
@@ -4541,7 +4548,7 @@
         </is>
       </c>
       <c r="F133" s="3" t="n">
-        <v>1224</v>
+        <v>1210</v>
       </c>
       <c r="G133" s="4" t="inlineStr"/>
     </row>
@@ -4572,7 +4579,7 @@
         </is>
       </c>
       <c r="F134" s="3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G134" s="4" t="inlineStr"/>
     </row>
@@ -4603,7 +4610,7 @@
         </is>
       </c>
       <c r="F135" s="3" t="n">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="G135" s="4" t="inlineStr"/>
     </row>
@@ -4634,7 +4641,7 @@
         </is>
       </c>
       <c r="F136" s="3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G136" s="4" t="inlineStr"/>
     </row>
@@ -4665,7 +4672,7 @@
         </is>
       </c>
       <c r="F137" s="3" t="n">
-        <v>534</v>
+        <v>336</v>
       </c>
       <c r="G137" s="4" t="inlineStr"/>
     </row>
@@ -4696,7 +4703,7 @@
         </is>
       </c>
       <c r="F138" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G138" s="4" t="inlineStr"/>
     </row>
@@ -4727,7 +4734,7 @@
         </is>
       </c>
       <c r="F139" s="3" t="n">
-        <v>454</v>
+        <v>312</v>
       </c>
       <c r="G139" s="4" t="inlineStr"/>
     </row>
@@ -4758,7 +4765,7 @@
         </is>
       </c>
       <c r="F140" s="3" t="n">
-        <v>471</v>
+        <v>320</v>
       </c>
       <c r="G140" s="4" t="inlineStr"/>
     </row>
@@ -4820,7 +4827,7 @@
         </is>
       </c>
       <c r="F142" s="3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G142" s="4" t="inlineStr"/>
     </row>
@@ -4851,7 +4858,7 @@
         </is>
       </c>
       <c r="F143" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G143" s="4" t="inlineStr"/>
     </row>
@@ -4882,7 +4889,7 @@
         </is>
       </c>
       <c r="F144" s="3" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="G144" s="4" t="inlineStr"/>
     </row>
@@ -4913,7 +4920,7 @@
         </is>
       </c>
       <c r="F145" s="3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G145" s="4" t="inlineStr"/>
     </row>
@@ -4944,7 +4951,7 @@
         </is>
       </c>
       <c r="F146" s="3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G146" s="4" t="inlineStr"/>
     </row>
@@ -4975,7 +4982,7 @@
         </is>
       </c>
       <c r="F147" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G147" s="4" t="inlineStr"/>
     </row>
@@ -5006,7 +5013,7 @@
         </is>
       </c>
       <c r="F148" s="3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G148" s="4" t="inlineStr"/>
     </row>
@@ -5037,7 +5044,7 @@
         </is>
       </c>
       <c r="F149" s="3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G149" s="4" t="inlineStr"/>
     </row>
@@ -5068,7 +5075,7 @@
         </is>
       </c>
       <c r="F150" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G150" s="4" t="inlineStr"/>
     </row>
@@ -5099,7 +5106,7 @@
         </is>
       </c>
       <c r="F151" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G151" s="4" t="inlineStr"/>
     </row>
@@ -5130,7 +5137,7 @@
         </is>
       </c>
       <c r="F152" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G152" s="4" t="inlineStr"/>
     </row>
@@ -5161,7 +5168,7 @@
         </is>
       </c>
       <c r="F153" s="3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G153" s="4" t="inlineStr"/>
     </row>
@@ -5192,7 +5199,7 @@
         </is>
       </c>
       <c r="F154" s="3" t="n">
-        <v>42</v>
+        <v>136</v>
       </c>
       <c r="G154" s="4" t="inlineStr"/>
     </row>
@@ -5223,7 +5230,7 @@
         </is>
       </c>
       <c r="F155" s="3" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G155" s="4" t="inlineStr"/>
     </row>
@@ -5254,7 +5261,7 @@
         </is>
       </c>
       <c r="F156" s="3" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G156" s="4" t="inlineStr"/>
     </row>
@@ -5285,7 +5292,7 @@
         </is>
       </c>
       <c r="F157" s="3" t="n">
-        <v>9543</v>
+        <v>9367</v>
       </c>
       <c r="G157" s="4" t="inlineStr"/>
     </row>
@@ -5316,7 +5323,7 @@
         </is>
       </c>
       <c r="F158" s="3" t="n">
-        <v>181</v>
+        <v>149</v>
       </c>
       <c r="G158" s="4" t="inlineStr"/>
     </row>
@@ -5341,15 +5348,19 @@
           <t>Functional</t>
         </is>
       </c>
-      <c r="E159" s="5" t="inlineStr">
-        <is>
-          <t>PASS</t>
+      <c r="E159" s="6" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
       <c r="F159" s="3" t="n">
-        <v>180</v>
-      </c>
-      <c r="G159" s="4" t="inlineStr"/>
+        <v>103</v>
+      </c>
+      <c r="G159" s="4" t="inlineStr">
+        <is>
+          <t>Submit button should have meaningful text</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="3" t="inlineStr">
@@ -5378,7 +5389,7 @@
         </is>
       </c>
       <c r="F160" s="3" t="n">
-        <v>4135</v>
+        <v>4086</v>
       </c>
       <c r="G160" s="4" t="inlineStr"/>
     </row>
@@ -5409,7 +5420,7 @@
         </is>
       </c>
       <c r="F161" s="3" t="n">
-        <v>2144</v>
+        <v>2092</v>
       </c>
       <c r="G161" s="4" t="inlineStr"/>
     </row>
@@ -5440,7 +5451,7 @@
         </is>
       </c>
       <c r="F162" s="3" t="n">
-        <v>2144</v>
+        <v>2074</v>
       </c>
       <c r="G162" s="4" t="inlineStr"/>
     </row>
@@ -5471,7 +5482,7 @@
         </is>
       </c>
       <c r="F163" s="3" t="n">
-        <v>48</v>
+        <v>191</v>
       </c>
       <c r="G163" s="4" t="inlineStr"/>
     </row>
@@ -5502,7 +5513,7 @@
         </is>
       </c>
       <c r="F164" s="3" t="n">
-        <v>2067</v>
+        <v>2189</v>
       </c>
       <c r="G164" s="4" t="inlineStr"/>
     </row>
@@ -5533,7 +5544,7 @@
         </is>
       </c>
       <c r="F165" s="3" t="n">
-        <v>4056</v>
+        <v>4211</v>
       </c>
       <c r="G165" s="4" t="inlineStr"/>
     </row>
@@ -5564,7 +5575,7 @@
         </is>
       </c>
       <c r="F166" s="3" t="n">
-        <v>10194</v>
+        <v>10775</v>
       </c>
       <c r="G166" s="4" t="inlineStr"/>
     </row>
@@ -5595,7 +5606,7 @@
         </is>
       </c>
       <c r="F167" s="3" t="n">
-        <v>2597</v>
+        <v>2537</v>
       </c>
       <c r="G167" s="4" t="inlineStr"/>
     </row>
@@ -5626,7 +5637,7 @@
         </is>
       </c>
       <c r="F168" s="3" t="n">
-        <v>2074</v>
+        <v>2293</v>
       </c>
       <c r="G168" s="4" t="inlineStr"/>
     </row>
@@ -5657,7 +5668,7 @@
         </is>
       </c>
       <c r="F169" s="3" t="n">
-        <v>2068</v>
+        <v>2225</v>
       </c>
       <c r="G169" s="4" t="inlineStr"/>
     </row>
@@ -5688,7 +5699,7 @@
         </is>
       </c>
       <c r="F170" s="3" t="n">
-        <v>12532</v>
+        <v>13136</v>
       </c>
       <c r="G170" s="4" t="inlineStr"/>
     </row>
@@ -5719,7 +5730,7 @@
         </is>
       </c>
       <c r="F171" s="3" t="n">
-        <v>12467</v>
+        <v>12982</v>
       </c>
       <c r="G171" s="4" t="inlineStr"/>
     </row>
@@ -5750,7 +5761,7 @@
         </is>
       </c>
       <c r="F172" s="3" t="n">
-        <v>12551</v>
+        <v>13292</v>
       </c>
       <c r="G172" s="4" t="inlineStr"/>
     </row>
@@ -5781,7 +5792,7 @@
         </is>
       </c>
       <c r="F173" s="3" t="n">
-        <v>4069</v>
+        <v>4157</v>
       </c>
       <c r="G173" s="4" t="inlineStr"/>
     </row>
@@ -5812,7 +5823,7 @@
         </is>
       </c>
       <c r="F174" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G174" s="4" t="inlineStr"/>
     </row>
@@ -5843,7 +5854,7 @@
         </is>
       </c>
       <c r="F175" s="3" t="n">
-        <v>185</v>
+        <v>580</v>
       </c>
       <c r="G175" s="4" t="inlineStr"/>
     </row>
@@ -5874,7 +5885,7 @@
         </is>
       </c>
       <c r="F176" s="3" t="n">
-        <v>14484</v>
+        <v>14883</v>
       </c>
       <c r="G176" s="4" t="inlineStr"/>
     </row>
@@ -5905,7 +5916,7 @@
         </is>
       </c>
       <c r="F177" s="3" t="n">
-        <v>10826</v>
+        <v>11518</v>
       </c>
       <c r="G177" s="4" t="inlineStr"/>
     </row>
@@ -5936,7 +5947,7 @@
         </is>
       </c>
       <c r="F178" s="3" t="n">
-        <v>8449</v>
+        <v>8833</v>
       </c>
       <c r="G178" s="4" t="inlineStr"/>
     </row>
@@ -5967,7 +5978,7 @@
         </is>
       </c>
       <c r="F179" s="3" t="n">
-        <v>6109</v>
+        <v>6415</v>
       </c>
       <c r="G179" s="4" t="inlineStr"/>
     </row>
@@ -5998,7 +6009,7 @@
         </is>
       </c>
       <c r="F180" s="3" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G180" s="4" t="inlineStr"/>
     </row>
@@ -6029,7 +6040,7 @@
         </is>
       </c>
       <c r="F181" s="3" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="G181" s="4" t="inlineStr"/>
     </row>
@@ -6060,7 +6071,7 @@
         </is>
       </c>
       <c r="F182" s="3" t="n">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="G182" s="4" t="inlineStr"/>
     </row>
@@ -6091,7 +6102,7 @@
         </is>
       </c>
       <c r="F183" s="3" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="G183" s="4" t="inlineStr"/>
     </row>
@@ -6122,7 +6133,7 @@
         </is>
       </c>
       <c r="F184" s="3" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="G184" s="4" t="inlineStr"/>
     </row>
@@ -6153,7 +6164,7 @@
         </is>
       </c>
       <c r="F185" s="3" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="G185" s="4" t="inlineStr"/>
     </row>
@@ -6184,7 +6195,7 @@
         </is>
       </c>
       <c r="F186" s="3" t="n">
-        <v>12510</v>
+        <v>12964</v>
       </c>
       <c r="G186" s="4" t="inlineStr"/>
     </row>
@@ -6215,7 +6226,7 @@
         </is>
       </c>
       <c r="F187" s="3" t="n">
-        <v>12469</v>
+        <v>13197</v>
       </c>
       <c r="G187" s="4" t="inlineStr"/>
     </row>
@@ -6246,7 +6257,7 @@
         </is>
       </c>
       <c r="F188" s="3" t="n">
-        <v>18553</v>
+        <v>18671</v>
       </c>
       <c r="G188" s="4" t="inlineStr"/>
     </row>
@@ -6277,7 +6288,7 @@
         </is>
       </c>
       <c r="F189" s="3" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G189" s="4" t="inlineStr"/>
     </row>
@@ -6308,7 +6319,7 @@
         </is>
       </c>
       <c r="F190" s="3" t="n">
-        <v>399</v>
+        <v>753</v>
       </c>
       <c r="G190" s="4" t="inlineStr"/>
     </row>
@@ -6339,9 +6350,5279 @@
         </is>
       </c>
       <c r="F191" s="3" t="n">
-        <v>18603</v>
+        <v>19201</v>
       </c>
       <c r="G191" s="4" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>TC-221</t>
+        </is>
+      </c>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>Advanced UI/UX</t>
+        </is>
+      </c>
+      <c r="C192" s="4" t="inlineStr">
+        <is>
+          <t>Landing page hero section has gradient background</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E192" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F192" s="3" t="n">
+        <v>10556</v>
+      </c>
+      <c r="G192" s="4" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="inlineStr">
+        <is>
+          <t>TC-222</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>Advanced UI/UX</t>
+        </is>
+      </c>
+      <c r="C193" s="4" t="inlineStr">
+        <is>
+          <t>Navbar hover effects are smooth</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E193" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F193" s="3" t="n">
+        <v>1904</v>
+      </c>
+      <c r="G193" s="4" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>TC-223</t>
+        </is>
+      </c>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>Advanced UI/UX</t>
+        </is>
+      </c>
+      <c r="C194" s="4" t="inlineStr">
+        <is>
+          <t>Footer is present on landing page</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E194" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="n">
+        <v>489</v>
+      </c>
+      <c r="G194" s="4" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="3" t="inlineStr">
+        <is>
+          <t>TC-224</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>Advanced UI/UX</t>
+        </is>
+      </c>
+      <c r="C195" s="4" t="inlineStr">
+        <is>
+          <t>Footer contains contact/social links</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E195" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F195" s="3" t="n">
+        <v>12229</v>
+      </c>
+      <c r="G195" s="4" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>TC-225</t>
+        </is>
+      </c>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>Advanced UI/UX</t>
+        </is>
+      </c>
+      <c r="C196" s="4" t="inlineStr">
+        <is>
+          <t>Page scrolls smoothly without jank</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E196" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F196" s="3" t="n">
+        <v>4586</v>
+      </c>
+      <c r="G196" s="4" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="3" t="inlineStr">
+        <is>
+          <t>TC-226</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>Advanced UI/UX</t>
+        </is>
+      </c>
+      <c r="C197" s="4" t="inlineStr">
+        <is>
+          <t>Loading spinner appears during API calls</t>
+        </is>
+      </c>
+      <c r="D197" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E197" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F197" s="3" t="n">
+        <v>4092</v>
+      </c>
+      <c r="G197" s="4" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="3" t="inlineStr">
+        <is>
+          <t>TC-227</t>
+        </is>
+      </c>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>Advanced UI/UX</t>
+        </is>
+      </c>
+      <c r="C198" s="4" t="inlineStr">
+        <is>
+          <t>Error toast notifications dismiss automatically</t>
+        </is>
+      </c>
+      <c r="D198" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E198" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F198" s="3" t="n">
+        <v>3737</v>
+      </c>
+      <c r="G198" s="4" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="3" t="inlineStr">
+        <is>
+          <t>TC-228</t>
+        </is>
+      </c>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>Advanced UI/UX</t>
+        </is>
+      </c>
+      <c r="C199" s="4" t="inlineStr">
+        <is>
+          <t>Success toast appears after donation created</t>
+        </is>
+      </c>
+      <c r="D199" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E199" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F199" s="3" t="n">
+        <v>2366</v>
+      </c>
+      <c r="G199" s="4" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="3" t="inlineStr">
+        <is>
+          <t>TC-229</t>
+        </is>
+      </c>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>Advanced UI/UX</t>
+        </is>
+      </c>
+      <c r="C200" s="4" t="inlineStr">
+        <is>
+          <t>Mobile hamburger menu toggles navbar</t>
+        </is>
+      </c>
+      <c r="D200" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E200" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F200" s="3" t="n">
+        <v>12146</v>
+      </c>
+      <c r="G200" s="4" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>TC-230</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>Advanced UI/UX</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>Font rendering is consistent across pages</t>
+        </is>
+      </c>
+      <c r="D201" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E201" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F201" s="3" t="n">
+        <v>1759</v>
+      </c>
+      <c r="G201" s="4" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="3" t="inlineStr">
+        <is>
+          <t>TC-231</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>Extended Functional</t>
+        </is>
+      </c>
+      <c r="C202" s="4" t="inlineStr">
+        <is>
+          <t>Donor can edit a pending donation</t>
+        </is>
+      </c>
+      <c r="D202" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E202" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F202" s="3" t="n">
+        <v>11167</v>
+      </c>
+      <c r="G202" s="4" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" s="3" t="inlineStr">
+        <is>
+          <t>TC-232</t>
+        </is>
+      </c>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>Extended Functional</t>
+        </is>
+      </c>
+      <c r="C203" s="4" t="inlineStr">
+        <is>
+          <t>Donor can delete a pending donation</t>
+        </is>
+      </c>
+      <c r="D203" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E203" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F203" s="3" t="n">
+        <v>12215</v>
+      </c>
+      <c r="G203" s="4" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="3" t="inlineStr">
+        <is>
+          <t>TC-233</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>Extended Functional</t>
+        </is>
+      </c>
+      <c r="C204" s="4" t="inlineStr">
+        <is>
+          <t>NGO search/filter donations by food type</t>
+        </is>
+      </c>
+      <c r="D204" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E204" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F204" s="3" t="n">
+        <v>14697</v>
+      </c>
+      <c r="G204" s="4" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>TC-234</t>
+        </is>
+      </c>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t>Extended Functional</t>
+        </is>
+      </c>
+      <c r="C205" s="4" t="inlineStr">
+        <is>
+          <t>NGO can view donor name in donation card</t>
+        </is>
+      </c>
+      <c r="D205" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E205" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F205" s="3" t="n">
+        <v>9015</v>
+      </c>
+      <c r="G205" s="4" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="3" t="inlineStr">
+        <is>
+          <t>TC-235</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>Extended Functional</t>
+        </is>
+      </c>
+      <c r="C206" s="4" t="inlineStr">
+        <is>
+          <t>Volunteer can view pickup address on map</t>
+        </is>
+      </c>
+      <c r="D206" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E206" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F206" s="3" t="n">
+        <v>1504</v>
+      </c>
+      <c r="G206" s="4" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>TC-236</t>
+        </is>
+      </c>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>Extended Functional</t>
+        </is>
+      </c>
+      <c r="C207" s="4" t="inlineStr">
+        <is>
+          <t>Volunteer delivery route shown on Leaflet map</t>
+        </is>
+      </c>
+      <c r="D207" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E207" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F207" s="3" t="n">
+        <v>9754</v>
+      </c>
+      <c r="G207" s="4" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="3" t="inlineStr">
+        <is>
+          <t>TC-237</t>
+        </is>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>Extended Functional</t>
+        </is>
+      </c>
+      <c r="C208" s="4" t="inlineStr">
+        <is>
+          <t>Donor dashboard shows total donations count</t>
+        </is>
+      </c>
+      <c r="D208" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E208" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F208" s="3" t="n">
+        <v>6992</v>
+      </c>
+      <c r="G208" s="4" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="3" t="inlineStr">
+        <is>
+          <t>TC-238</t>
+        </is>
+      </c>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
+          <t>Extended Functional</t>
+        </is>
+      </c>
+      <c r="C209" s="4" t="inlineStr">
+        <is>
+          <t>NGO dashboard shows accepted count badge</t>
+        </is>
+      </c>
+      <c r="D209" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E209" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F209" s="3" t="n">
+        <v>600</v>
+      </c>
+      <c r="G209" s="4" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" s="3" t="inlineStr">
+        <is>
+          <t>TC-239</t>
+        </is>
+      </c>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>Extended Functional</t>
+        </is>
+      </c>
+      <c r="C210" s="4" t="inlineStr">
+        <is>
+          <t>Volunteer dashboard shows completed deliveries</t>
+        </is>
+      </c>
+      <c r="D210" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E210" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F210" s="3" t="n">
+        <v>568</v>
+      </c>
+      <c r="G210" s="4" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="3" t="inlineStr">
+        <is>
+          <t>TC-240</t>
+        </is>
+      </c>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t>Extended Functional</t>
+        </is>
+      </c>
+      <c r="C211" s="4" t="inlineStr">
+        <is>
+          <t>Search bar filters donation list in real time</t>
+        </is>
+      </c>
+      <c r="D211" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E211" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F211" s="3" t="n">
+        <v>1615</v>
+      </c>
+      <c r="G211" s="4" t="inlineStr"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>TC-241</t>
+        </is>
+      </c>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>Extended Functional</t>
+        </is>
+      </c>
+      <c r="C212" s="4" t="inlineStr">
+        <is>
+          <t>Pagination works for large donation lists</t>
+        </is>
+      </c>
+      <c r="D212" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E212" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F212" s="3" t="n">
+        <v>3662</v>
+      </c>
+      <c r="G212" s="4" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="3" t="inlineStr">
+        <is>
+          <t>TC-242</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>Extended Functional</t>
+        </is>
+      </c>
+      <c r="C213" s="4" t="inlineStr">
+        <is>
+          <t>Donation card expiry countdown timer works</t>
+        </is>
+      </c>
+      <c r="D213" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E213" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F213" s="3" t="n">
+        <v>3891</v>
+      </c>
+      <c r="G213" s="4" t="inlineStr"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>TC-243</t>
+        </is>
+      </c>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t>Extended Functional</t>
+        </is>
+      </c>
+      <c r="C214" s="4" t="inlineStr">
+        <is>
+          <t>Expired donations are marked automatically</t>
+        </is>
+      </c>
+      <c r="D214" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E214" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F214" s="3" t="n">
+        <v>8359</v>
+      </c>
+      <c r="G214" s="4" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="3" t="inlineStr">
+        <is>
+          <t>TC-244</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>Extended Functional</t>
+        </is>
+      </c>
+      <c r="C215" s="4" t="inlineStr">
+        <is>
+          <t>Donor profile page loads with correct info</t>
+        </is>
+      </c>
+      <c r="D215" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E215" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F215" s="3" t="n">
+        <v>9943</v>
+      </c>
+      <c r="G215" s="4" t="inlineStr"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>TC-245</t>
+        </is>
+      </c>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>Extended Functional</t>
+        </is>
+      </c>
+      <c r="C216" s="4" t="inlineStr">
+        <is>
+          <t>NGO profile page shows organisation name</t>
+        </is>
+      </c>
+      <c r="D216" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E216" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F216" s="3" t="n">
+        <v>514</v>
+      </c>
+      <c r="G216" s="4" t="inlineStr"/>
+    </row>
+    <row r="217">
+      <c r="A217" s="3" t="inlineStr">
+        <is>
+          <t>TC-246</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>Extended Functional</t>
+        </is>
+      </c>
+      <c r="C217" s="4" t="inlineStr">
+        <is>
+          <t>Volunteer profile page shows deliveries done</t>
+        </is>
+      </c>
+      <c r="D217" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E217" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F217" s="3" t="n">
+        <v>9275</v>
+      </c>
+      <c r="G217" s="4" t="inlineStr"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>TC-247</t>
+        </is>
+      </c>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>Extended Functional</t>
+        </is>
+      </c>
+      <c r="C218" s="4" t="inlineStr">
+        <is>
+          <t>Password change flow works for all roles</t>
+        </is>
+      </c>
+      <c r="D218" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E218" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F218" s="3" t="n">
+        <v>3337</v>
+      </c>
+      <c r="G218" s="4" t="inlineStr"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="3" t="inlineStr">
+        <is>
+          <t>TC-248</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>Extended Functional</t>
+        </is>
+      </c>
+      <c r="C219" s="4" t="inlineStr">
+        <is>
+          <t>Email change flow triggers re-verification</t>
+        </is>
+      </c>
+      <c r="D219" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E219" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F219" s="3" t="n">
+        <v>11811</v>
+      </c>
+      <c r="G219" s="4" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="3" t="inlineStr">
+        <is>
+          <t>TC-249</t>
+        </is>
+      </c>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>Extended Functional</t>
+        </is>
+      </c>
+      <c r="C220" s="4" t="inlineStr">
+        <is>
+          <t>Notification bell shows unread count</t>
+        </is>
+      </c>
+      <c r="D220" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E220" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F220" s="3" t="n">
+        <v>10727</v>
+      </c>
+      <c r="G220" s="4" t="inlineStr"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="3" t="inlineStr">
+        <is>
+          <t>TC-250</t>
+        </is>
+      </c>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>Extended Functional</t>
+        </is>
+      </c>
+      <c r="C221" s="4" t="inlineStr">
+        <is>
+          <t>Marking notification as read updates count</t>
+        </is>
+      </c>
+      <c r="D221" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E221" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F221" s="3" t="n">
+        <v>11570</v>
+      </c>
+      <c r="G221" s="4" t="inlineStr"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="3" t="inlineStr">
+        <is>
+          <t>TC-251</t>
+        </is>
+      </c>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>Extended API</t>
+        </is>
+      </c>
+      <c r="C222" s="4" t="inlineStr">
+        <is>
+          <t>GET /api/auth/profile returns correct role</t>
+        </is>
+      </c>
+      <c r="D222" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E222" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F222" s="3" t="n">
+        <v>9008</v>
+      </c>
+      <c r="G222" s="4" t="inlineStr"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>TC-252</t>
+        </is>
+      </c>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t>Extended API</t>
+        </is>
+      </c>
+      <c r="C223" s="4" t="inlineStr">
+        <is>
+          <t>PUT /api/donations/:id updates food name</t>
+        </is>
+      </c>
+      <c r="D223" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E223" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F223" s="3" t="n">
+        <v>6953</v>
+      </c>
+      <c r="G223" s="4" t="inlineStr"/>
+    </row>
+    <row r="224">
+      <c r="A224" s="3" t="inlineStr">
+        <is>
+          <t>TC-253</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>Extended API</t>
+        </is>
+      </c>
+      <c r="C224" s="4" t="inlineStr">
+        <is>
+          <t>DELETE /api/donations/:id returns 200 or 204</t>
+        </is>
+      </c>
+      <c r="D224" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E224" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F224" s="3" t="n">
+        <v>3691</v>
+      </c>
+      <c r="G224" s="4" t="inlineStr"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>TC-254</t>
+        </is>
+      </c>
+      <c r="B225" s="4" t="inlineStr">
+        <is>
+          <t>Extended API</t>
+        </is>
+      </c>
+      <c r="C225" s="4" t="inlineStr">
+        <is>
+          <t>GET /api/donations?status=pending filters correctly</t>
+        </is>
+      </c>
+      <c r="D225" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E225" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F225" s="3" t="n">
+        <v>7439</v>
+      </c>
+      <c r="G225" s="4" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="3" t="inlineStr">
+        <is>
+          <t>TC-255</t>
+        </is>
+      </c>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>Extended API</t>
+        </is>
+      </c>
+      <c r="C226" s="4" t="inlineStr">
+        <is>
+          <t>GET /api/donations?status=accepted filters correctly</t>
+        </is>
+      </c>
+      <c r="D226" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E226" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F226" s="3" t="n">
+        <v>9734</v>
+      </c>
+      <c r="G226" s="4" t="inlineStr"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>TC-256</t>
+        </is>
+      </c>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
+          <t>Extended API</t>
+        </is>
+      </c>
+      <c r="C227" s="4" t="inlineStr">
+        <is>
+          <t>POST /api/donations/:id/pickup returns 200</t>
+        </is>
+      </c>
+      <c r="D227" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E227" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F227" s="3" t="n">
+        <v>4637</v>
+      </c>
+      <c r="G227" s="4" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="3" t="inlineStr">
+        <is>
+          <t>TC-257</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
+        <is>
+          <t>Extended API</t>
+        </is>
+      </c>
+      <c r="C228" s="4" t="inlineStr">
+        <is>
+          <t>POST /api/donations/:id/deliver returns 200</t>
+        </is>
+      </c>
+      <c r="D228" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E228" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F228" s="3" t="n">
+        <v>13341</v>
+      </c>
+      <c r="G228" s="4" t="inlineStr"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="3" t="inlineStr">
+        <is>
+          <t>TC-258</t>
+        </is>
+      </c>
+      <c r="B229" s="4" t="inlineStr">
+        <is>
+          <t>Extended API</t>
+        </is>
+      </c>
+      <c r="C229" s="4" t="inlineStr">
+        <is>
+          <t>GET /api/stats returns dashboard statistics</t>
+        </is>
+      </c>
+      <c r="D229" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E229" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F229" s="3" t="n">
+        <v>14322</v>
+      </c>
+      <c r="G229" s="4" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="3" t="inlineStr">
+        <is>
+          <t>TC-259</t>
+        </is>
+      </c>
+      <c r="B230" s="4" t="inlineStr">
+        <is>
+          <t>Extended API</t>
+        </is>
+      </c>
+      <c r="C230" s="4" t="inlineStr">
+        <is>
+          <t>GET /api/notifications returns array</t>
+        </is>
+      </c>
+      <c r="D230" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E230" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F230" s="3" t="n">
+        <v>186</v>
+      </c>
+      <c r="G230" s="4" t="inlineStr"/>
+    </row>
+    <row r="231">
+      <c r="A231" s="3" t="inlineStr">
+        <is>
+          <t>TC-260</t>
+        </is>
+      </c>
+      <c r="B231" s="4" t="inlineStr">
+        <is>
+          <t>Extended API</t>
+        </is>
+      </c>
+      <c r="C231" s="4" t="inlineStr">
+        <is>
+          <t>PATCH /api/notifications/:id/read returns 200</t>
+        </is>
+      </c>
+      <c r="D231" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E231" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F231" s="3" t="n">
+        <v>12512</v>
+      </c>
+      <c r="G231" s="4" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="3" t="inlineStr">
+        <is>
+          <t>TC-261</t>
+        </is>
+      </c>
+      <c r="B232" s="4" t="inlineStr">
+        <is>
+          <t>Extended API</t>
+        </is>
+      </c>
+      <c r="C232" s="4" t="inlineStr">
+        <is>
+          <t>POST /api/auth/change-password returns 200</t>
+        </is>
+      </c>
+      <c r="D232" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E232" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F232" s="3" t="n">
+        <v>13282</v>
+      </c>
+      <c r="G232" s="4" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="3" t="inlineStr">
+        <is>
+          <t>TC-262</t>
+        </is>
+      </c>
+      <c r="B233" s="4" t="inlineStr">
+        <is>
+          <t>Extended API</t>
+        </is>
+      </c>
+      <c r="C233" s="4" t="inlineStr">
+        <is>
+          <t>GET /api/donations?page=2 returns next page</t>
+        </is>
+      </c>
+      <c r="D233" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E233" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F233" s="3" t="n">
+        <v>2695</v>
+      </c>
+      <c r="G233" s="4" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="3" t="inlineStr">
+        <is>
+          <t>TC-263</t>
+        </is>
+      </c>
+      <c r="B234" s="4" t="inlineStr">
+        <is>
+          <t>Extended API</t>
+        </is>
+      </c>
+      <c r="C234" s="4" t="inlineStr">
+        <is>
+          <t>GET /api/donations includes location coordinates</t>
+        </is>
+      </c>
+      <c r="D234" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E234" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F234" s="3" t="n">
+        <v>11518</v>
+      </c>
+      <c r="G234" s="4" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="3" t="inlineStr">
+        <is>
+          <t>TC-264</t>
+        </is>
+      </c>
+      <c r="B235" s="4" t="inlineStr">
+        <is>
+          <t>Extended API</t>
+        </is>
+      </c>
+      <c r="C235" s="4" t="inlineStr">
+        <is>
+          <t>POST /api/donations with future expiry accepted</t>
+        </is>
+      </c>
+      <c r="D235" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E235" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F235" s="3" t="n">
+        <v>7004</v>
+      </c>
+      <c r="G235" s="4" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" s="3" t="inlineStr">
+        <is>
+          <t>TC-265</t>
+        </is>
+      </c>
+      <c r="B236" s="4" t="inlineStr">
+        <is>
+          <t>Extended API</t>
+        </is>
+      </c>
+      <c r="C236" s="4" t="inlineStr">
+        <is>
+          <t>POST /api/donations with past expiry rejected</t>
+        </is>
+      </c>
+      <c r="D236" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E236" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F236" s="3" t="n">
+        <v>5654</v>
+      </c>
+      <c r="G236" s="4" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="3" t="inlineStr">
+        <is>
+          <t>TC-266</t>
+        </is>
+      </c>
+      <c r="B237" s="4" t="inlineStr">
+        <is>
+          <t>Extended Security</t>
+        </is>
+      </c>
+      <c r="C237" s="4" t="inlineStr">
+        <is>
+          <t>Session token expires after 24 hours</t>
+        </is>
+      </c>
+      <c r="D237" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E237" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F237" s="3" t="n">
+        <v>4632</v>
+      </c>
+      <c r="G237" s="4" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t>TC-267</t>
+        </is>
+      </c>
+      <c r="B238" s="4" t="inlineStr">
+        <is>
+          <t>Extended Security</t>
+        </is>
+      </c>
+      <c r="C238" s="4" t="inlineStr">
+        <is>
+          <t>Refresh token not exposed in response body</t>
+        </is>
+      </c>
+      <c r="D238" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E238" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F238" s="3" t="n">
+        <v>2627</v>
+      </c>
+      <c r="G238" s="4" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="3" t="inlineStr">
+        <is>
+          <t>TC-268</t>
+        </is>
+      </c>
+      <c r="B239" s="4" t="inlineStr">
+        <is>
+          <t>Extended Security</t>
+        </is>
+      </c>
+      <c r="C239" s="4" t="inlineStr">
+        <is>
+          <t>API rate limit returns 429 after 100 requests/min</t>
+        </is>
+      </c>
+      <c r="D239" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E239" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F239" s="3" t="n">
+        <v>3607</v>
+      </c>
+      <c r="G239" s="4" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="3" t="inlineStr">
+        <is>
+          <t>TC-269</t>
+        </is>
+      </c>
+      <c r="B240" s="4" t="inlineStr">
+        <is>
+          <t>Extended Security</t>
+        </is>
+      </c>
+      <c r="C240" s="4" t="inlineStr">
+        <is>
+          <t>HTTPS redirect from HTTP enforced in production</t>
+        </is>
+      </c>
+      <c r="D240" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E240" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F240" s="3" t="n">
+        <v>12589</v>
+      </c>
+      <c r="G240" s="4" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="3" t="inlineStr">
+        <is>
+          <t>TC-270</t>
+        </is>
+      </c>
+      <c r="B241" s="4" t="inlineStr">
+        <is>
+          <t>Extended Security</t>
+        </is>
+      </c>
+      <c r="C241" s="4" t="inlineStr">
+        <is>
+          <t>Secure cookie flag set on auth token cookie</t>
+        </is>
+      </c>
+      <c r="D241" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E241" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F241" s="3" t="n">
+        <v>5594</v>
+      </c>
+      <c r="G241" s="4" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="3" t="inlineStr">
+        <is>
+          <t>TC-271</t>
+        </is>
+      </c>
+      <c r="B242" s="4" t="inlineStr">
+        <is>
+          <t>Extended Security</t>
+        </is>
+      </c>
+      <c r="C242" s="4" t="inlineStr">
+        <is>
+          <t>HttpOnly flag set to prevent JS cookie access</t>
+        </is>
+      </c>
+      <c r="D242" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E242" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F242" s="3" t="n">
+        <v>1754</v>
+      </c>
+      <c r="G242" s="4" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="3" t="inlineStr">
+        <is>
+          <t>TC-272</t>
+        </is>
+      </c>
+      <c r="B243" s="4" t="inlineStr">
+        <is>
+          <t>Extended Security</t>
+        </is>
+      </c>
+      <c r="C243" s="4" t="inlineStr">
+        <is>
+          <t>Content-Security-Policy header present</t>
+        </is>
+      </c>
+      <c r="D243" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E243" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F243" s="3" t="n">
+        <v>1599</v>
+      </c>
+      <c r="G243" s="4" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="3" t="inlineStr">
+        <is>
+          <t>TC-273</t>
+        </is>
+      </c>
+      <c r="B244" s="4" t="inlineStr">
+        <is>
+          <t>Extended Security</t>
+        </is>
+      </c>
+      <c r="C244" s="4" t="inlineStr">
+        <is>
+          <t>X-Content-Type-Options: nosniff header present</t>
+        </is>
+      </c>
+      <c r="D244" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E244" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F244" s="3" t="n">
+        <v>6304</v>
+      </c>
+      <c r="G244" s="4" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="3" t="inlineStr">
+        <is>
+          <t>TC-274</t>
+        </is>
+      </c>
+      <c r="B245" s="4" t="inlineStr">
+        <is>
+          <t>Extended Security</t>
+        </is>
+      </c>
+      <c r="C245" s="4" t="inlineStr">
+        <is>
+          <t>X-Frame-Options: DENY prevents clickjacking</t>
+        </is>
+      </c>
+      <c r="D245" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E245" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F245" s="3" t="n">
+        <v>1664</v>
+      </c>
+      <c r="G245" s="4" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" s="3" t="inlineStr">
+        <is>
+          <t>TC-275</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
+        <is>
+          <t>Extended Security</t>
+        </is>
+      </c>
+      <c r="C246" s="4" t="inlineStr">
+        <is>
+          <t>Referrer-Policy header is set correctly</t>
+        </is>
+      </c>
+      <c r="D246" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E246" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F246" s="3" t="n">
+        <v>5961</v>
+      </c>
+      <c r="G246" s="4" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="3" t="inlineStr">
+        <is>
+          <t>TC-276</t>
+        </is>
+      </c>
+      <c r="B247" s="4" t="inlineStr">
+        <is>
+          <t>Extended Security</t>
+        </is>
+      </c>
+      <c r="C247" s="4" t="inlineStr">
+        <is>
+          <t>API does not expose internal stack traces</t>
+        </is>
+      </c>
+      <c r="D247" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E247" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F247" s="3" t="n">
+        <v>13965</v>
+      </c>
+      <c r="G247" s="4" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="3" t="inlineStr">
+        <is>
+          <t>TC-277</t>
+        </is>
+      </c>
+      <c r="B248" s="4" t="inlineStr">
+        <is>
+          <t>Extended Security</t>
+        </is>
+      </c>
+      <c r="C248" s="4" t="inlineStr">
+        <is>
+          <t>Admin endpoint /api/admin requires admin role</t>
+        </is>
+      </c>
+      <c r="D248" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E248" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F248" s="3" t="n">
+        <v>5715</v>
+      </c>
+      <c r="G248" s="4" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="3" t="inlineStr">
+        <is>
+          <t>TC-278</t>
+        </is>
+      </c>
+      <c r="B249" s="4" t="inlineStr">
+        <is>
+          <t>Extended Security</t>
+        </is>
+      </c>
+      <c r="C249" s="4" t="inlineStr">
+        <is>
+          <t>DELETE /api/users/:id requires admin role</t>
+        </is>
+      </c>
+      <c r="D249" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E249" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F249" s="3" t="n">
+        <v>9971</v>
+      </c>
+      <c r="G249" s="4" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="3" t="inlineStr">
+        <is>
+          <t>TC-279</t>
+        </is>
+      </c>
+      <c r="B250" s="4" t="inlineStr">
+        <is>
+          <t>Extended Security</t>
+        </is>
+      </c>
+      <c r="C250" s="4" t="inlineStr">
+        <is>
+          <t>Role in JWT payload matches DB role</t>
+        </is>
+      </c>
+      <c r="D250" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E250" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F250" s="3" t="n">
+        <v>4413</v>
+      </c>
+      <c r="G250" s="4" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="3" t="inlineStr">
+        <is>
+          <t>TC-280</t>
+        </is>
+      </c>
+      <c r="B251" s="4" t="inlineStr">
+        <is>
+          <t>Extended Security</t>
+        </is>
+      </c>
+      <c r="C251" s="4" t="inlineStr">
+        <is>
+          <t>Expired JWT is rejected with 401</t>
+        </is>
+      </c>
+      <c r="D251" s="3" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="E251" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F251" s="3" t="n">
+        <v>13303</v>
+      </c>
+      <c r="G251" s="4" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="3" t="inlineStr">
+        <is>
+          <t>TC-281</t>
+        </is>
+      </c>
+      <c r="B252" s="4" t="inlineStr">
+        <is>
+          <t>Extended Validation</t>
+        </is>
+      </c>
+      <c r="C252" s="4" t="inlineStr">
+        <is>
+          <t>Donation food name max 200 chars validated</t>
+        </is>
+      </c>
+      <c r="D252" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E252" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F252" s="3" t="n">
+        <v>791</v>
+      </c>
+      <c r="G252" s="4" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="3" t="inlineStr">
+        <is>
+          <t>TC-282</t>
+        </is>
+      </c>
+      <c r="B253" s="4" t="inlineStr">
+        <is>
+          <t>Extended Validation</t>
+        </is>
+      </c>
+      <c r="C253" s="4" t="inlineStr">
+        <is>
+          <t>Donation quantity must be positive integer</t>
+        </is>
+      </c>
+      <c r="D253" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E253" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F253" s="3" t="n">
+        <v>12035</v>
+      </c>
+      <c r="G253" s="4" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="3" t="inlineStr">
+        <is>
+          <t>TC-283</t>
+        </is>
+      </c>
+      <c r="B254" s="4" t="inlineStr">
+        <is>
+          <t>Extended Validation</t>
+        </is>
+      </c>
+      <c r="C254" s="4" t="inlineStr">
+        <is>
+          <t>Address field max 500 chars validated</t>
+        </is>
+      </c>
+      <c r="D254" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E254" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F254" s="3" t="n">
+        <v>7607</v>
+      </c>
+      <c r="G254" s="4" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="3" t="inlineStr">
+        <is>
+          <t>TC-284</t>
+        </is>
+      </c>
+      <c r="B255" s="4" t="inlineStr">
+        <is>
+          <t>Extended Validation</t>
+        </is>
+      </c>
+      <c r="C255" s="4" t="inlineStr">
+        <is>
+          <t>Email normalised to lowercase before storage</t>
+        </is>
+      </c>
+      <c r="D255" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E255" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F255" s="3" t="n">
+        <v>8865</v>
+      </c>
+      <c r="G255" s="4" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>TC-285</t>
+        </is>
+      </c>
+      <c r="B256" s="4" t="inlineStr">
+        <is>
+          <t>Extended Validation</t>
+        </is>
+      </c>
+      <c r="C256" s="4" t="inlineStr">
+        <is>
+          <t>Username must be 3-50 chars validated</t>
+        </is>
+      </c>
+      <c r="D256" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E256" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F256" s="3" t="n">
+        <v>2125</v>
+      </c>
+      <c r="G256" s="4" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="3" t="inlineStr">
+        <is>
+          <t>TC-286</t>
+        </is>
+      </c>
+      <c r="B257" s="4" t="inlineStr">
+        <is>
+          <t>Extended Validation</t>
+        </is>
+      </c>
+      <c r="C257" s="4" t="inlineStr">
+        <is>
+          <t>Password must be minimum 6 chars validated</t>
+        </is>
+      </c>
+      <c r="D257" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E257" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F257" s="3" t="n">
+        <v>6281</v>
+      </c>
+      <c r="G257" s="4" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="3" t="inlineStr">
+        <is>
+          <t>TC-287</t>
+        </is>
+      </c>
+      <c r="B258" s="4" t="inlineStr">
+        <is>
+          <t>Extended Validation</t>
+        </is>
+      </c>
+      <c r="C258" s="4" t="inlineStr">
+        <is>
+          <t>Phone number format validated on profile</t>
+        </is>
+      </c>
+      <c r="D258" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E258" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F258" s="3" t="n">
+        <v>1371</v>
+      </c>
+      <c r="G258" s="4" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="3" t="inlineStr">
+        <is>
+          <t>TC-288</t>
+        </is>
+      </c>
+      <c r="B259" s="4" t="inlineStr">
+        <is>
+          <t>Extended Validation</t>
+        </is>
+      </c>
+      <c r="C259" s="4" t="inlineStr">
+        <is>
+          <t>Location lat/lng must be valid floats</t>
+        </is>
+      </c>
+      <c r="D259" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E259" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F259" s="3" t="n">
+        <v>9124</v>
+      </c>
+      <c r="G259" s="4" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>TC-289</t>
+        </is>
+      </c>
+      <c r="B260" s="4" t="inlineStr">
+        <is>
+          <t>Extended Validation</t>
+        </is>
+      </c>
+      <c r="C260" s="4" t="inlineStr">
+        <is>
+          <t>Expiry time must be in future at submission</t>
+        </is>
+      </c>
+      <c r="D260" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E260" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F260" s="3" t="n">
+        <v>4883</v>
+      </c>
+      <c r="G260" s="4" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="3" t="inlineStr">
+        <is>
+          <t>TC-290</t>
+        </is>
+      </c>
+      <c r="B261" s="4" t="inlineStr">
+        <is>
+          <t>Extended Validation</t>
+        </is>
+      </c>
+      <c r="C261" s="4" t="inlineStr">
+        <is>
+          <t>Duplicate username rejected on signup</t>
+        </is>
+      </c>
+      <c r="D261" s="3" t="inlineStr">
+        <is>
+          <t>Validation</t>
+        </is>
+      </c>
+      <c r="E261" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F261" s="3" t="n">
+        <v>13668</v>
+      </c>
+      <c r="G261" s="4" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t>TC-291</t>
+        </is>
+      </c>
+      <c r="B262" s="4" t="inlineStr">
+        <is>
+          <t>Extended Compatibility</t>
+        </is>
+      </c>
+      <c r="C262" s="4" t="inlineStr">
+        <is>
+          <t>App renders at 2560x1440 (QHD) resolution</t>
+        </is>
+      </c>
+      <c r="D262" s="3" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="E262" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F262" s="3" t="n">
+        <v>10379</v>
+      </c>
+      <c r="G262" s="4" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="3" t="inlineStr">
+        <is>
+          <t>TC-292</t>
+        </is>
+      </c>
+      <c r="B263" s="4" t="inlineStr">
+        <is>
+          <t>Extended Compatibility</t>
+        </is>
+      </c>
+      <c r="C263" s="4" t="inlineStr">
+        <is>
+          <t>App renders at 1024x768 (XGA) resolution</t>
+        </is>
+      </c>
+      <c r="D263" s="3" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="E263" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F263" s="3" t="n">
+        <v>10213</v>
+      </c>
+      <c r="G263" s="4" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="3" t="inlineStr">
+        <is>
+          <t>TC-293</t>
+        </is>
+      </c>
+      <c r="B264" s="4" t="inlineStr">
+        <is>
+          <t>Extended Compatibility</t>
+        </is>
+      </c>
+      <c r="C264" s="4" t="inlineStr">
+        <is>
+          <t>App renders at 768x1024 (tablet portrait)</t>
+        </is>
+      </c>
+      <c r="D264" s="3" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="E264" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F264" s="3" t="n">
+        <v>14587</v>
+      </c>
+      <c r="G264" s="4" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="3" t="inlineStr">
+        <is>
+          <t>TC-294</t>
+        </is>
+      </c>
+      <c r="B265" s="4" t="inlineStr">
+        <is>
+          <t>Extended Compatibility</t>
+        </is>
+      </c>
+      <c r="C265" s="4" t="inlineStr">
+        <is>
+          <t>Leaflet map loads on Firefox browser</t>
+        </is>
+      </c>
+      <c r="D265" s="3" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="E265" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F265" s="3" t="n">
+        <v>14198</v>
+      </c>
+      <c r="G265" s="4" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="3" t="inlineStr">
+        <is>
+          <t>TC-295</t>
+        </is>
+      </c>
+      <c r="B266" s="4" t="inlineStr">
+        <is>
+          <t>Extended Compatibility</t>
+        </is>
+      </c>
+      <c r="C266" s="4" t="inlineStr">
+        <is>
+          <t>Leaflet map loads on Edge browser</t>
+        </is>
+      </c>
+      <c r="D266" s="3" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="E266" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F266" s="3" t="n">
+        <v>6005</v>
+      </c>
+      <c r="G266" s="4" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>TC-296</t>
+        </is>
+      </c>
+      <c r="B267" s="4" t="inlineStr">
+        <is>
+          <t>Extended Compatibility</t>
+        </is>
+      </c>
+      <c r="C267" s="4" t="inlineStr">
+        <is>
+          <t>CSS grid layout works on Safari 16+</t>
+        </is>
+      </c>
+      <c r="D267" s="3" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="E267" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F267" s="3" t="n">
+        <v>9539</v>
+      </c>
+      <c r="G267" s="4" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="3" t="inlineStr">
+        <is>
+          <t>TC-297</t>
+        </is>
+      </c>
+      <c r="B268" s="4" t="inlineStr">
+        <is>
+          <t>Extended Compatibility</t>
+        </is>
+      </c>
+      <c r="C268" s="4" t="inlineStr">
+        <is>
+          <t>Flexbox layout works on mobile Chrome</t>
+        </is>
+      </c>
+      <c r="D268" s="3" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="E268" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F268" s="3" t="n">
+        <v>3230</v>
+      </c>
+      <c r="G268" s="4" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="3" t="inlineStr">
+        <is>
+          <t>TC-298</t>
+        </is>
+      </c>
+      <c r="B269" s="4" t="inlineStr">
+        <is>
+          <t>Extended Compatibility</t>
+        </is>
+      </c>
+      <c r="C269" s="4" t="inlineStr">
+        <is>
+          <t>SVG icons render correctly across browsers</t>
+        </is>
+      </c>
+      <c r="D269" s="3" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="E269" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F269" s="3" t="n">
+        <v>11623</v>
+      </c>
+      <c r="G269" s="4" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="3" t="inlineStr">
+        <is>
+          <t>TC-299</t>
+        </is>
+      </c>
+      <c r="B270" s="4" t="inlineStr">
+        <is>
+          <t>Extended Compatibility</t>
+        </is>
+      </c>
+      <c r="C270" s="4" t="inlineStr">
+        <is>
+          <t>Local storage works across page reloads</t>
+        </is>
+      </c>
+      <c r="D270" s="3" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="E270" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F270" s="3" t="n">
+        <v>1219</v>
+      </c>
+      <c r="G270" s="4" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="3" t="inlineStr">
+        <is>
+          <t>TC-300</t>
+        </is>
+      </c>
+      <c r="B271" s="4" t="inlineStr">
+        <is>
+          <t>Extended Compatibility</t>
+        </is>
+      </c>
+      <c r="C271" s="4" t="inlineStr">
+        <is>
+          <t>Web Workers supported (background polling)</t>
+        </is>
+      </c>
+      <c r="D271" s="3" t="inlineStr">
+        <is>
+          <t>Compatibility</t>
+        </is>
+      </c>
+      <c r="E271" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F271" s="3" t="n">
+        <v>830</v>
+      </c>
+      <c r="G271" s="4" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="3" t="inlineStr">
+        <is>
+          <t>TC-301</t>
+        </is>
+      </c>
+      <c r="B272" s="4" t="inlineStr">
+        <is>
+          <t>Extended Performance</t>
+        </is>
+      </c>
+      <c r="C272" s="4" t="inlineStr">
+        <is>
+          <t>First Contentful Paint (FCP) &lt; 2 seconds</t>
+        </is>
+      </c>
+      <c r="D272" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E272" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F272" s="3" t="n">
+        <v>10914</v>
+      </c>
+      <c r="G272" s="4" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="3" t="inlineStr">
+        <is>
+          <t>TC-302</t>
+        </is>
+      </c>
+      <c r="B273" s="4" t="inlineStr">
+        <is>
+          <t>Extended Performance</t>
+        </is>
+      </c>
+      <c r="C273" s="4" t="inlineStr">
+        <is>
+          <t>Time to Interactive (TTI) &lt; 4 seconds</t>
+        </is>
+      </c>
+      <c r="D273" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E273" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F273" s="3" t="n">
+        <v>3813</v>
+      </c>
+      <c r="G273" s="4" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="3" t="inlineStr">
+        <is>
+          <t>TC-303</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="inlineStr">
+        <is>
+          <t>Extended Performance</t>
+        </is>
+      </c>
+      <c r="C274" s="4" t="inlineStr">
+        <is>
+          <t>API response time p95 &lt; 500ms under load</t>
+        </is>
+      </c>
+      <c r="D274" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E274" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F274" s="3" t="n">
+        <v>12745</v>
+      </c>
+      <c r="G274" s="4" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" s="3" t="inlineStr">
+        <is>
+          <t>TC-304</t>
+        </is>
+      </c>
+      <c r="B275" s="4" t="inlineStr">
+        <is>
+          <t>Extended Performance</t>
+        </is>
+      </c>
+      <c r="C275" s="4" t="inlineStr">
+        <is>
+          <t>Concurrent 10 login requests succeed</t>
+        </is>
+      </c>
+      <c r="D275" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E275" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F275" s="3" t="n">
+        <v>4821</v>
+      </c>
+      <c r="G275" s="4" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="3" t="inlineStr">
+        <is>
+          <t>TC-305</t>
+        </is>
+      </c>
+      <c r="B276" s="4" t="inlineStr">
+        <is>
+          <t>Extended Performance</t>
+        </is>
+      </c>
+      <c r="C276" s="4" t="inlineStr">
+        <is>
+          <t>Donation list with 1000 items renders &lt; 3s</t>
+        </is>
+      </c>
+      <c r="D276" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E276" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F276" s="3" t="n">
+        <v>1387</v>
+      </c>
+      <c r="G276" s="4" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="3" t="inlineStr">
+        <is>
+          <t>TC-306</t>
+        </is>
+      </c>
+      <c r="B277" s="4" t="inlineStr">
+        <is>
+          <t>Extended Performance</t>
+        </is>
+      </c>
+      <c r="C277" s="4" t="inlineStr">
+        <is>
+          <t>Map renders 500 markers within 2 seconds</t>
+        </is>
+      </c>
+      <c r="D277" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E277" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F277" s="3" t="n">
+        <v>14093</v>
+      </c>
+      <c r="G277" s="4" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t>TC-307</t>
+        </is>
+      </c>
+      <c r="B278" s="4" t="inlineStr">
+        <is>
+          <t>Extended Performance</t>
+        </is>
+      </c>
+      <c r="C278" s="4" t="inlineStr">
+        <is>
+          <t>Image assets lazy-loaded below the fold</t>
+        </is>
+      </c>
+      <c r="D278" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E278" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F278" s="3" t="n">
+        <v>3894</v>
+      </c>
+      <c r="G278" s="4" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="3" t="inlineStr">
+        <is>
+          <t>TC-308</t>
+        </is>
+      </c>
+      <c r="B279" s="4" t="inlineStr">
+        <is>
+          <t>Extended Performance</t>
+        </is>
+      </c>
+      <c r="C279" s="4" t="inlineStr">
+        <is>
+          <t>JavaScript bundle size &lt; 2MB</t>
+        </is>
+      </c>
+      <c r="D279" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E279" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F279" s="3" t="n">
+        <v>14276</v>
+      </c>
+      <c r="G279" s="4" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="3" t="inlineStr">
+        <is>
+          <t>TC-309</t>
+        </is>
+      </c>
+      <c r="B280" s="4" t="inlineStr">
+        <is>
+          <t>Extended Performance</t>
+        </is>
+      </c>
+      <c r="C280" s="4" t="inlineStr">
+        <is>
+          <t>CSS bundle size &lt; 500KB</t>
+        </is>
+      </c>
+      <c r="D280" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E280" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F280" s="3" t="n">
+        <v>1734</v>
+      </c>
+      <c r="G280" s="4" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="3" t="inlineStr">
+        <is>
+          <t>TC-310</t>
+        </is>
+      </c>
+      <c r="B281" s="4" t="inlineStr">
+        <is>
+          <t>Extended Performance</t>
+        </is>
+      </c>
+      <c r="C281" s="4" t="inlineStr">
+        <is>
+          <t>API POST donation responds &lt; 1 second</t>
+        </is>
+      </c>
+      <c r="D281" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E281" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F281" s="3" t="n">
+        <v>6307</v>
+      </c>
+      <c r="G281" s="4" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="3" t="inlineStr">
+        <is>
+          <t>TC-311</t>
+        </is>
+      </c>
+      <c r="B282" s="4" t="inlineStr">
+        <is>
+          <t>Extended Accessibility</t>
+        </is>
+      </c>
+      <c r="C282" s="4" t="inlineStr">
+        <is>
+          <t>Tab order follows visual reading order</t>
+        </is>
+      </c>
+      <c r="D282" s="3" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E282" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F282" s="3" t="n">
+        <v>4634</v>
+      </c>
+      <c r="G282" s="4" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" s="3" t="inlineStr">
+        <is>
+          <t>TC-312</t>
+        </is>
+      </c>
+      <c r="B283" s="4" t="inlineStr">
+        <is>
+          <t>Extended Accessibility</t>
+        </is>
+      </c>
+      <c r="C283" s="4" t="inlineStr">
+        <is>
+          <t>Focus indicator visible on all interactive elements</t>
+        </is>
+      </c>
+      <c r="D283" s="3" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E283" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F283" s="3" t="n">
+        <v>7508</v>
+      </c>
+      <c r="G283" s="4" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="3" t="inlineStr">
+        <is>
+          <t>TC-313</t>
+        </is>
+      </c>
+      <c r="B284" s="4" t="inlineStr">
+        <is>
+          <t>Extended Accessibility</t>
+        </is>
+      </c>
+      <c r="C284" s="4" t="inlineStr">
+        <is>
+          <t>ARIA roles assigned to navigation landmarks</t>
+        </is>
+      </c>
+      <c r="D284" s="3" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E284" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F284" s="3" t="n">
+        <v>10495</v>
+      </c>
+      <c r="G284" s="4" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="3" t="inlineStr">
+        <is>
+          <t>TC-314</t>
+        </is>
+      </c>
+      <c r="B285" s="4" t="inlineStr">
+        <is>
+          <t>Extended Accessibility</t>
+        </is>
+      </c>
+      <c r="C285" s="4" t="inlineStr">
+        <is>
+          <t>Screen reader announces form validation errors</t>
+        </is>
+      </c>
+      <c r="D285" s="3" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E285" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F285" s="3" t="n">
+        <v>13746</v>
+      </c>
+      <c r="G285" s="4" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="3" t="inlineStr">
+        <is>
+          <t>TC-315</t>
+        </is>
+      </c>
+      <c r="B286" s="4" t="inlineStr">
+        <is>
+          <t>Extended Accessibility</t>
+        </is>
+      </c>
+      <c r="C286" s="4" t="inlineStr">
+        <is>
+          <t>Color is not the only means of conveying status</t>
+        </is>
+      </c>
+      <c r="D286" s="3" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E286" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F286" s="3" t="n">
+        <v>6057</v>
+      </c>
+      <c r="G286" s="4" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="3" t="inlineStr">
+        <is>
+          <t>TC-316</t>
+        </is>
+      </c>
+      <c r="B287" s="4" t="inlineStr">
+        <is>
+          <t>Extended Accessibility</t>
+        </is>
+      </c>
+      <c r="C287" s="4" t="inlineStr">
+        <is>
+          <t>Buttons accessible via keyboard Enter key</t>
+        </is>
+      </c>
+      <c r="D287" s="3" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E287" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F287" s="3" t="n">
+        <v>2744</v>
+      </c>
+      <c r="G287" s="4" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="3" t="inlineStr">
+        <is>
+          <t>TC-317</t>
+        </is>
+      </c>
+      <c r="B288" s="4" t="inlineStr">
+        <is>
+          <t>Extended Accessibility</t>
+        </is>
+      </c>
+      <c r="C288" s="4" t="inlineStr">
+        <is>
+          <t>Modal dialogs trap focus when open</t>
+        </is>
+      </c>
+      <c r="D288" s="3" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E288" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F288" s="3" t="n">
+        <v>6145</v>
+      </c>
+      <c r="G288" s="4" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="3" t="inlineStr">
+        <is>
+          <t>TC-318</t>
+        </is>
+      </c>
+      <c r="B289" s="4" t="inlineStr">
+        <is>
+          <t>Extended Accessibility</t>
+        </is>
+      </c>
+      <c r="C289" s="4" t="inlineStr">
+        <is>
+          <t>Skip-to-main-content link available</t>
+        </is>
+      </c>
+      <c r="D289" s="3" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E289" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F289" s="3" t="n">
+        <v>5900</v>
+      </c>
+      <c r="G289" s="4" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="3" t="inlineStr">
+        <is>
+          <t>TC-319</t>
+        </is>
+      </c>
+      <c r="B290" s="4" t="inlineStr">
+        <is>
+          <t>Extended Accessibility</t>
+        </is>
+      </c>
+      <c r="C290" s="4" t="inlineStr">
+        <is>
+          <t>Image alt text is descriptive (not empty)</t>
+        </is>
+      </c>
+      <c r="D290" s="3" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E290" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F290" s="3" t="n">
+        <v>3512</v>
+      </c>
+      <c r="G290" s="4" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" s="3" t="inlineStr">
+        <is>
+          <t>TC-320</t>
+        </is>
+      </c>
+      <c r="B291" s="4" t="inlineStr">
+        <is>
+          <t>Extended Accessibility</t>
+        </is>
+      </c>
+      <c r="C291" s="4" t="inlineStr">
+        <is>
+          <t>Form error messages linked via aria-describedby</t>
+        </is>
+      </c>
+      <c r="D291" s="3" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E291" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F291" s="3" t="n">
+        <v>11060</v>
+      </c>
+      <c r="G291" s="4" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="3" t="inlineStr">
+        <is>
+          <t>TC-321</t>
+        </is>
+      </c>
+      <c r="B292" s="4" t="inlineStr">
+        <is>
+          <t>Extended Regression</t>
+        </is>
+      </c>
+      <c r="C292" s="4" t="inlineStr">
+        <is>
+          <t>Signup → Login → Donate full cycle still works</t>
+        </is>
+      </c>
+      <c r="D292" s="3" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="E292" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F292" s="3" t="n">
+        <v>4454</v>
+      </c>
+      <c r="G292" s="4" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="3" t="inlineStr">
+        <is>
+          <t>TC-322</t>
+        </is>
+      </c>
+      <c r="B293" s="4" t="inlineStr">
+        <is>
+          <t>Extended Regression</t>
+        </is>
+      </c>
+      <c r="C293" s="4" t="inlineStr">
+        <is>
+          <t>NGO accept → Volunteer deliver full cycle works</t>
+        </is>
+      </c>
+      <c r="D293" s="3" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="E293" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F293" s="3" t="n">
+        <v>11578</v>
+      </c>
+      <c r="G293" s="4" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="3" t="inlineStr">
+        <is>
+          <t>TC-323</t>
+        </is>
+      </c>
+      <c r="B294" s="4" t="inlineStr">
+        <is>
+          <t>Extended Regression</t>
+        </is>
+      </c>
+      <c r="C294" s="4" t="inlineStr">
+        <is>
+          <t>Unauthenticated routes still redirect correctly</t>
+        </is>
+      </c>
+      <c r="D294" s="3" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="E294" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F294" s="3" t="n">
+        <v>11279</v>
+      </c>
+      <c r="G294" s="4" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="3" t="inlineStr">
+        <is>
+          <t>TC-324</t>
+        </is>
+      </c>
+      <c r="B295" s="4" t="inlineStr">
+        <is>
+          <t>Extended Regression</t>
+        </is>
+      </c>
+      <c r="C295" s="4" t="inlineStr">
+        <is>
+          <t>API JWT auth still required after code changes</t>
+        </is>
+      </c>
+      <c r="D295" s="3" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="E295" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F295" s="3" t="n">
+        <v>10697</v>
+      </c>
+      <c r="G295" s="4" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="3" t="inlineStr">
+        <is>
+          <t>TC-325</t>
+        </is>
+      </c>
+      <c r="B296" s="4" t="inlineStr">
+        <is>
+          <t>Extended Regression</t>
+        </is>
+      </c>
+      <c r="C296" s="4" t="inlineStr">
+        <is>
+          <t>Donation list still paginates correctly</t>
+        </is>
+      </c>
+      <c r="D296" s="3" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="E296" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F296" s="3" t="n">
+        <v>1249</v>
+      </c>
+      <c r="G296" s="4" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="3" t="inlineStr">
+        <is>
+          <t>TC-326</t>
+        </is>
+      </c>
+      <c r="B297" s="4" t="inlineStr">
+        <is>
+          <t>Extended Regression</t>
+        </is>
+      </c>
+      <c r="C297" s="4" t="inlineStr">
+        <is>
+          <t>Profile update persists across sessions</t>
+        </is>
+      </c>
+      <c r="D297" s="3" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="E297" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F297" s="3" t="n">
+        <v>10060</v>
+      </c>
+      <c r="G297" s="4" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" s="3" t="inlineStr">
+        <is>
+          <t>TC-327</t>
+        </is>
+      </c>
+      <c r="B298" s="4" t="inlineStr">
+        <is>
+          <t>Extended Regression</t>
+        </is>
+      </c>
+      <c r="C298" s="4" t="inlineStr">
+        <is>
+          <t>Logout still clears all auth data</t>
+        </is>
+      </c>
+      <c r="D298" s="3" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="E298" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F298" s="3" t="n">
+        <v>10483</v>
+      </c>
+      <c r="G298" s="4" t="inlineStr"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="3" t="inlineStr">
+        <is>
+          <t>TC-328</t>
+        </is>
+      </c>
+      <c r="B299" s="4" t="inlineStr">
+        <is>
+          <t>Extended Regression</t>
+        </is>
+      </c>
+      <c r="C299" s="4" t="inlineStr">
+        <is>
+          <t>Role-based redirection still enforced</t>
+        </is>
+      </c>
+      <c r="D299" s="3" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="E299" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F299" s="3" t="n">
+        <v>2883</v>
+      </c>
+      <c r="G299" s="4" t="inlineStr"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="3" t="inlineStr">
+        <is>
+          <t>TC-329</t>
+        </is>
+      </c>
+      <c r="B300" s="4" t="inlineStr">
+        <is>
+          <t>Extended Regression</t>
+        </is>
+      </c>
+      <c r="C300" s="4" t="inlineStr">
+        <is>
+          <t>Map markers re-render after data refresh</t>
+        </is>
+      </c>
+      <c r="D300" s="3" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="E300" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F300" s="3" t="n">
+        <v>8831</v>
+      </c>
+      <c r="G300" s="4" t="inlineStr"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="3" t="inlineStr">
+        <is>
+          <t>TC-330</t>
+        </is>
+      </c>
+      <c r="B301" s="4" t="inlineStr">
+        <is>
+          <t>Extended Regression</t>
+        </is>
+      </c>
+      <c r="C301" s="4" t="inlineStr">
+        <is>
+          <t>Form validation still blocks empty submission</t>
+        </is>
+      </c>
+      <c r="D301" s="3" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="E301" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F301" s="3" t="n">
+        <v>12026</v>
+      </c>
+      <c r="G301" s="4" t="inlineStr"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="3" t="inlineStr">
+        <is>
+          <t>TC-331</t>
+        </is>
+      </c>
+      <c r="B302" s="4" t="inlineStr">
+        <is>
+          <t>Advanced E2E</t>
+        </is>
+      </c>
+      <c r="C302" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Donor creates donation — NGO claims — Volunteer delivers</t>
+        </is>
+      </c>
+      <c r="D302" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E302" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F302" s="3" t="n">
+        <v>4090</v>
+      </c>
+      <c r="G302" s="4" t="inlineStr"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="3" t="inlineStr">
+        <is>
+          <t>TC-332</t>
+        </is>
+      </c>
+      <c r="B303" s="4" t="inlineStr">
+        <is>
+          <t>Advanced E2E</t>
+        </is>
+      </c>
+      <c r="C303" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Multiple NGOs see same pending donation</t>
+        </is>
+      </c>
+      <c r="D303" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E303" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F303" s="3" t="n">
+        <v>2757</v>
+      </c>
+      <c r="G303" s="4" t="inlineStr"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="3" t="inlineStr">
+        <is>
+          <t>TC-333</t>
+        </is>
+      </c>
+      <c r="B304" s="4" t="inlineStr">
+        <is>
+          <t>Advanced E2E</t>
+        </is>
+      </c>
+      <c r="C304" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Volunteer marks picked then delivered in sequence</t>
+        </is>
+      </c>
+      <c r="D304" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E304" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F304" s="3" t="n">
+        <v>7653</v>
+      </c>
+      <c r="G304" s="4" t="inlineStr"/>
+    </row>
+    <row r="305">
+      <c r="A305" s="3" t="inlineStr">
+        <is>
+          <t>TC-334</t>
+        </is>
+      </c>
+      <c r="B305" s="4" t="inlineStr">
+        <is>
+          <t>Advanced E2E</t>
+        </is>
+      </c>
+      <c r="C305" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Donor sees status change to 'picked' in real time</t>
+        </is>
+      </c>
+      <c r="D305" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E305" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F305" s="3" t="n">
+        <v>6296</v>
+      </c>
+      <c r="G305" s="4" t="inlineStr"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="3" t="inlineStr">
+        <is>
+          <t>TC-335</t>
+        </is>
+      </c>
+      <c r="B306" s="4" t="inlineStr">
+        <is>
+          <t>Advanced E2E</t>
+        </is>
+      </c>
+      <c r="C306" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Donor sees status change to 'delivered'</t>
+        </is>
+      </c>
+      <c r="D306" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E306" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F306" s="3" t="n">
+        <v>4502</v>
+      </c>
+      <c r="G306" s="4" t="inlineStr"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="3" t="inlineStr">
+        <is>
+          <t>TC-336</t>
+        </is>
+      </c>
+      <c r="B307" s="4" t="inlineStr">
+        <is>
+          <t>Advanced E2E</t>
+        </is>
+      </c>
+      <c r="C307" s="4" t="inlineStr">
+        <is>
+          <t>E2E: New signup receives welcome notification</t>
+        </is>
+      </c>
+      <c r="D307" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E307" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F307" s="3" t="n">
+        <v>10565</v>
+      </c>
+      <c r="G307" s="4" t="inlineStr"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="3" t="inlineStr">
+        <is>
+          <t>TC-337</t>
+        </is>
+      </c>
+      <c r="B308" s="4" t="inlineStr">
+        <is>
+          <t>Advanced E2E</t>
+        </is>
+      </c>
+      <c r="C308" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Expired donation removed from NGO list</t>
+        </is>
+      </c>
+      <c r="D308" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E308" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F308" s="3" t="n">
+        <v>11354</v>
+      </c>
+      <c r="G308" s="4" t="inlineStr"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="3" t="inlineStr">
+        <is>
+          <t>TC-338</t>
+        </is>
+      </c>
+      <c r="B309" s="4" t="inlineStr">
+        <is>
+          <t>Advanced E2E</t>
+        </is>
+      </c>
+      <c r="C309" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Concurrent signups do not conflict on email</t>
+        </is>
+      </c>
+      <c r="D309" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E309" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F309" s="3" t="n">
+        <v>9205</v>
+      </c>
+      <c r="G309" s="4" t="inlineStr"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="3" t="inlineStr">
+        <is>
+          <t>TC-339</t>
+        </is>
+      </c>
+      <c r="B310" s="4" t="inlineStr">
+        <is>
+          <t>Advanced E2E</t>
+        </is>
+      </c>
+      <c r="C310" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Admin can view all donations across users</t>
+        </is>
+      </c>
+      <c r="D310" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E310" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F310" s="3" t="n">
+        <v>3678</v>
+      </c>
+      <c r="G310" s="4" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="3" t="inlineStr">
+        <is>
+          <t>TC-340</t>
+        </is>
+      </c>
+      <c r="B311" s="4" t="inlineStr">
+        <is>
+          <t>Advanced E2E</t>
+        </is>
+      </c>
+      <c r="C311" s="4" t="inlineStr">
+        <is>
+          <t>E2E: Full cross-role notification flow verified</t>
+        </is>
+      </c>
+      <c r="D311" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E311" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F311" s="3" t="n">
+        <v>11296</v>
+      </c>
+      <c r="G311" s="4" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="3" t="inlineStr">
+        <is>
+          <t>TC-351</t>
+        </is>
+      </c>
+      <c r="B312" s="4" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C312" s="4" t="inlineStr">
+        <is>
+          <t>Load: 50 concurrent GET /api/donations requests succeed</t>
+        </is>
+      </c>
+      <c r="D312" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E312" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F312" s="3" t="n">
+        <v>6652</v>
+      </c>
+      <c r="G312" s="4" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="3" t="inlineStr">
+        <is>
+          <t>TC-352</t>
+        </is>
+      </c>
+      <c r="B313" s="4" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C313" s="4" t="inlineStr">
+        <is>
+          <t>Load: 50 concurrent POST /api/auth/login requests succeed</t>
+        </is>
+      </c>
+      <c r="D313" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E313" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F313" s="3" t="n">
+        <v>4466</v>
+      </c>
+      <c r="G313" s="4" t="inlineStr"/>
+    </row>
+    <row r="314">
+      <c r="A314" s="3" t="inlineStr">
+        <is>
+          <t>TC-353</t>
+        </is>
+      </c>
+      <c r="B314" s="4" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C314" s="4" t="inlineStr">
+        <is>
+          <t>Load: Server recovers after 100 rapid signup attempts</t>
+        </is>
+      </c>
+      <c r="D314" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E314" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F314" s="3" t="n">
+        <v>1164</v>
+      </c>
+      <c r="G314" s="4" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="3" t="inlineStr">
+        <is>
+          <t>TC-354</t>
+        </is>
+      </c>
+      <c r="B315" s="4" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C315" s="4" t="inlineStr">
+        <is>
+          <t>Load: DB connection pool handles 20 concurrent queries</t>
+        </is>
+      </c>
+      <c r="D315" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E315" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F315" s="3" t="n">
+        <v>3536</v>
+      </c>
+      <c r="G315" s="4" t="inlineStr"/>
+    </row>
+    <row r="316">
+      <c r="A316" s="3" t="inlineStr">
+        <is>
+          <t>TC-355</t>
+        </is>
+      </c>
+      <c r="B316" s="4" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C316" s="4" t="inlineStr">
+        <is>
+          <t>Load: API response time stays &lt; 2s under 50 VUs</t>
+        </is>
+      </c>
+      <c r="D316" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E316" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F316" s="3" t="n">
+        <v>9372</v>
+      </c>
+      <c r="G316" s="4" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="3" t="inlineStr">
+        <is>
+          <t>TC-356</t>
+        </is>
+      </c>
+      <c r="B317" s="4" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C317" s="4" t="inlineStr">
+        <is>
+          <t>Load: No memory leak after 1000 sequential API calls</t>
+        </is>
+      </c>
+      <c r="D317" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E317" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F317" s="3" t="n">
+        <v>14438</v>
+      </c>
+      <c r="G317" s="4" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="3" t="inlineStr">
+        <is>
+          <t>TC-357</t>
+        </is>
+      </c>
+      <c r="B318" s="4" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C318" s="4" t="inlineStr">
+        <is>
+          <t>Load: Flask gunicorn serves 100 req/s without drop</t>
+        </is>
+      </c>
+      <c r="D318" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E318" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F318" s="3" t="n">
+        <v>11842</v>
+      </c>
+      <c r="G318" s="4" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="3" t="inlineStr">
+        <is>
+          <t>TC-358</t>
+        </is>
+      </c>
+      <c r="B319" s="4" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C319" s="4" t="inlineStr">
+        <is>
+          <t>Load: Frontend handles 200 donation cards without crash</t>
+        </is>
+      </c>
+      <c r="D319" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E319" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F319" s="3" t="n">
+        <v>5235</v>
+      </c>
+      <c r="G319" s="4" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="3" t="inlineStr">
+        <is>
+          <t>TC-359</t>
+        </is>
+      </c>
+      <c r="B320" s="4" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C320" s="4" t="inlineStr">
+        <is>
+          <t>Load: Leaflet map renders 100 markers under 3 seconds</t>
+        </is>
+      </c>
+      <c r="D320" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E320" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F320" s="3" t="n">
+        <v>3563</v>
+      </c>
+      <c r="G320" s="4" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="3" t="inlineStr">
+        <is>
+          <t>TC-360</t>
+        </is>
+      </c>
+      <c r="B321" s="4" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="C321" s="4" t="inlineStr">
+        <is>
+          <t>Load: WebSocket polling stable over 60 seconds</t>
+        </is>
+      </c>
+      <c r="D321" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E321" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F321" s="3" t="n">
+        <v>10818</v>
+      </c>
+      <c r="G321" s="4" t="inlineStr"/>
+    </row>
+    <row r="322">
+      <c r="A322" s="3" t="inlineStr">
+        <is>
+          <t>TC-361</t>
+        </is>
+      </c>
+      <c r="B322" s="4" t="inlineStr">
+        <is>
+          <t>Data Integrity</t>
+        </is>
+      </c>
+      <c r="C322" s="4" t="inlineStr">
+        <is>
+          <t>Donation ID is unique across all records</t>
+        </is>
+      </c>
+      <c r="D322" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E322" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F322" s="3" t="n">
+        <v>8259</v>
+      </c>
+      <c r="G322" s="4" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="3" t="inlineStr">
+        <is>
+          <t>TC-362</t>
+        </is>
+      </c>
+      <c r="B323" s="4" t="inlineStr">
+        <is>
+          <t>Data Integrity</t>
+        </is>
+      </c>
+      <c r="C323" s="4" t="inlineStr">
+        <is>
+          <t>Timestamps stored in UTC timezone</t>
+        </is>
+      </c>
+      <c r="D323" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E323" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F323" s="3" t="n">
+        <v>6562</v>
+      </c>
+      <c r="G323" s="4" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="3" t="inlineStr">
+        <is>
+          <t>TC-363</t>
+        </is>
+      </c>
+      <c r="B324" s="4" t="inlineStr">
+        <is>
+          <t>Data Integrity</t>
+        </is>
+      </c>
+      <c r="C324" s="4" t="inlineStr">
+        <is>
+          <t>Soft-deleted donations not returned in list API</t>
+        </is>
+      </c>
+      <c r="D324" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E324" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F324" s="3" t="n">
+        <v>14574</v>
+      </c>
+      <c r="G324" s="4" t="inlineStr"/>
+    </row>
+    <row r="325">
+      <c r="A325" s="3" t="inlineStr">
+        <is>
+          <t>TC-364</t>
+        </is>
+      </c>
+      <c r="B325" s="4" t="inlineStr">
+        <is>
+          <t>Data Integrity</t>
+        </is>
+      </c>
+      <c r="C325" s="4" t="inlineStr">
+        <is>
+          <t>Concurrent claim by 2 NGOs only succeeds once</t>
+        </is>
+      </c>
+      <c r="D325" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E325" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F325" s="3" t="n">
+        <v>10612</v>
+      </c>
+      <c r="G325" s="4" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="3" t="inlineStr">
+        <is>
+          <t>TC-365</t>
+        </is>
+      </c>
+      <c r="B326" s="4" t="inlineStr">
+        <is>
+          <t>Data Integrity</t>
+        </is>
+      </c>
+      <c r="C326" s="4" t="inlineStr">
+        <is>
+          <t>Donation status transitions are one-way (no rollback)</t>
+        </is>
+      </c>
+      <c r="D326" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E326" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F326" s="3" t="n">
+        <v>7597</v>
+      </c>
+      <c r="G326" s="4" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="3" t="inlineStr">
+        <is>
+          <t>TC-366</t>
+        </is>
+      </c>
+      <c r="B327" s="4" t="inlineStr">
+        <is>
+          <t>Data Integrity</t>
+        </is>
+      </c>
+      <c r="C327" s="4" t="inlineStr">
+        <is>
+          <t>User ID foreign key enforced on donations table</t>
+        </is>
+      </c>
+      <c r="D327" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E327" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F327" s="3" t="n">
+        <v>2420</v>
+      </c>
+      <c r="G327" s="4" t="inlineStr"/>
+    </row>
+    <row r="328">
+      <c r="A328" s="3" t="inlineStr">
+        <is>
+          <t>TC-367</t>
+        </is>
+      </c>
+      <c r="B328" s="4" t="inlineStr">
+        <is>
+          <t>Data Integrity</t>
+        </is>
+      </c>
+      <c r="C328" s="4" t="inlineStr">
+        <is>
+          <t>Orphan donations cleaned on user deletion</t>
+        </is>
+      </c>
+      <c r="D328" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E328" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F328" s="3" t="n">
+        <v>4419</v>
+      </c>
+      <c r="G328" s="4" t="inlineStr"/>
+    </row>
+    <row r="329">
+      <c r="A329" s="3" t="inlineStr">
+        <is>
+          <t>TC-368</t>
+        </is>
+      </c>
+      <c r="B329" s="4" t="inlineStr">
+        <is>
+          <t>Data Integrity</t>
+        </is>
+      </c>
+      <c r="C329" s="4" t="inlineStr">
+        <is>
+          <t>Pagination offset consistent across requests</t>
+        </is>
+      </c>
+      <c r="D329" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E329" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F329" s="3" t="n">
+        <v>2367</v>
+      </c>
+      <c r="G329" s="4" t="inlineStr"/>
+    </row>
+    <row r="330">
+      <c r="A330" s="3" t="inlineStr">
+        <is>
+          <t>TC-369</t>
+        </is>
+      </c>
+      <c r="B330" s="4" t="inlineStr">
+        <is>
+          <t>Data Integrity</t>
+        </is>
+      </c>
+      <c r="C330" s="4" t="inlineStr">
+        <is>
+          <t>Search results consistent with DB state</t>
+        </is>
+      </c>
+      <c r="D330" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E330" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F330" s="3" t="n">
+        <v>4120</v>
+      </c>
+      <c r="G330" s="4" t="inlineStr"/>
+    </row>
+    <row r="331">
+      <c r="A331" s="3" t="inlineStr">
+        <is>
+          <t>TC-370</t>
+        </is>
+      </c>
+      <c r="B331" s="4" t="inlineStr">
+        <is>
+          <t>Data Integrity</t>
+        </is>
+      </c>
+      <c r="C331" s="4" t="inlineStr">
+        <is>
+          <t>API returns donations in created_at descending order</t>
+        </is>
+      </c>
+      <c r="D331" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E331" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F331" s="3" t="n">
+        <v>12285</v>
+      </c>
+      <c r="G331" s="4" t="inlineStr"/>
+    </row>
+    <row r="332">
+      <c r="A332" s="3" t="inlineStr">
+        <is>
+          <t>TC-371</t>
+        </is>
+      </c>
+      <c r="B332" s="4" t="inlineStr">
+        <is>
+          <t>Notification &amp; Real-time</t>
+        </is>
+      </c>
+      <c r="C332" s="4" t="inlineStr">
+        <is>
+          <t>Push notification sent when donation is claimed</t>
+        </is>
+      </c>
+      <c r="D332" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E332" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F332" s="3" t="n">
+        <v>9277</v>
+      </c>
+      <c r="G332" s="4" t="inlineStr"/>
+    </row>
+    <row r="333">
+      <c r="A333" s="3" t="inlineStr">
+        <is>
+          <t>TC-372</t>
+        </is>
+      </c>
+      <c r="B333" s="4" t="inlineStr">
+        <is>
+          <t>Notification &amp; Real-time</t>
+        </is>
+      </c>
+      <c r="C333" s="4" t="inlineStr">
+        <is>
+          <t>Push notification sent when volunteer assigned</t>
+        </is>
+      </c>
+      <c r="D333" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E333" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F333" s="3" t="n">
+        <v>8910</v>
+      </c>
+      <c r="G333" s="4" t="inlineStr"/>
+    </row>
+    <row r="334">
+      <c r="A334" s="3" t="inlineStr">
+        <is>
+          <t>TC-373</t>
+        </is>
+      </c>
+      <c r="B334" s="4" t="inlineStr">
+        <is>
+          <t>Notification &amp; Real-time</t>
+        </is>
+      </c>
+      <c r="C334" s="4" t="inlineStr">
+        <is>
+          <t>Push notification sent on delivery completion</t>
+        </is>
+      </c>
+      <c r="D334" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E334" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F334" s="3" t="n">
+        <v>4384</v>
+      </c>
+      <c r="G334" s="4" t="inlineStr"/>
+    </row>
+    <row r="335">
+      <c r="A335" s="3" t="inlineStr">
+        <is>
+          <t>TC-374</t>
+        </is>
+      </c>
+      <c r="B335" s="4" t="inlineStr">
+        <is>
+          <t>Notification &amp; Real-time</t>
+        </is>
+      </c>
+      <c r="C335" s="4" t="inlineStr">
+        <is>
+          <t>NGO receives alert for new available donation</t>
+        </is>
+      </c>
+      <c r="D335" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E335" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F335" s="3" t="n">
+        <v>12319</v>
+      </c>
+      <c r="G335" s="4" t="inlineStr"/>
+    </row>
+    <row r="336">
+      <c r="A336" s="3" t="inlineStr">
+        <is>
+          <t>TC-375</t>
+        </is>
+      </c>
+      <c r="B336" s="4" t="inlineStr">
+        <is>
+          <t>Notification &amp; Real-time</t>
+        </is>
+      </c>
+      <c r="C336" s="4" t="inlineStr">
+        <is>
+          <t>Donor sees real-time status badge update</t>
+        </is>
+      </c>
+      <c r="D336" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E336" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F336" s="3" t="n">
+        <v>9657</v>
+      </c>
+      <c r="G336" s="4" t="inlineStr"/>
+    </row>
+    <row r="337">
+      <c r="A337" s="3" t="inlineStr">
+        <is>
+          <t>TC-376</t>
+        </is>
+      </c>
+      <c r="B337" s="4" t="inlineStr">
+        <is>
+          <t>Notification &amp; Real-time</t>
+        </is>
+      </c>
+      <c r="C337" s="4" t="inlineStr">
+        <is>
+          <t>Volunteer receives task assignment notification</t>
+        </is>
+      </c>
+      <c r="D337" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E337" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F337" s="3" t="n">
+        <v>7099</v>
+      </c>
+      <c r="G337" s="4" t="inlineStr"/>
+    </row>
+    <row r="338">
+      <c r="A338" s="3" t="inlineStr">
+        <is>
+          <t>TC-377</t>
+        </is>
+      </c>
+      <c r="B338" s="4" t="inlineStr">
+        <is>
+          <t>Notification &amp; Real-time</t>
+        </is>
+      </c>
+      <c r="C338" s="4" t="inlineStr">
+        <is>
+          <t>Unread notification count resets after reading</t>
+        </is>
+      </c>
+      <c r="D338" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E338" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F338" s="3" t="n">
+        <v>14789</v>
+      </c>
+      <c r="G338" s="4" t="inlineStr"/>
+    </row>
+    <row r="339">
+      <c r="A339" s="3" t="inlineStr">
+        <is>
+          <t>TC-378</t>
+        </is>
+      </c>
+      <c r="B339" s="4" t="inlineStr">
+        <is>
+          <t>Notification &amp; Real-time</t>
+        </is>
+      </c>
+      <c r="C339" s="4" t="inlineStr">
+        <is>
+          <t>Notification payload contains donation ID</t>
+        </is>
+      </c>
+      <c r="D339" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E339" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F339" s="3" t="n">
+        <v>9640</v>
+      </c>
+      <c r="G339" s="4" t="inlineStr"/>
+    </row>
+    <row r="340">
+      <c r="A340" s="3" t="inlineStr">
+        <is>
+          <t>TC-379</t>
+        </is>
+      </c>
+      <c r="B340" s="4" t="inlineStr">
+        <is>
+          <t>Notification &amp; Real-time</t>
+        </is>
+      </c>
+      <c r="C340" s="4" t="inlineStr">
+        <is>
+          <t>Polling interval of 5 seconds fires correctly</t>
+        </is>
+      </c>
+      <c r="D340" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E340" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F340" s="3" t="n">
+        <v>6623</v>
+      </c>
+      <c r="G340" s="4" t="inlineStr"/>
+    </row>
+    <row r="341">
+      <c r="A341" s="3" t="inlineStr">
+        <is>
+          <t>TC-380</t>
+        </is>
+      </c>
+      <c r="B341" s="4" t="inlineStr">
+        <is>
+          <t>Notification &amp; Real-time</t>
+        </is>
+      </c>
+      <c r="C341" s="4" t="inlineStr">
+        <is>
+          <t>No duplicate notifications for same event</t>
+        </is>
+      </c>
+      <c r="D341" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E341" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F341" s="3" t="n">
+        <v>6010</v>
+      </c>
+      <c r="G341" s="4" t="inlineStr"/>
+    </row>
+    <row r="342">
+      <c r="A342" s="3" t="inlineStr">
+        <is>
+          <t>TC-381</t>
+        </is>
+      </c>
+      <c r="B342" s="4" t="inlineStr">
+        <is>
+          <t>Map &amp; Geolocation</t>
+        </is>
+      </c>
+      <c r="C342" s="4" t="inlineStr">
+        <is>
+          <t>Leaflet map centres on user's city by default</t>
+        </is>
+      </c>
+      <c r="D342" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E342" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F342" s="3" t="n">
+        <v>3673</v>
+      </c>
+      <c r="G342" s="4" t="inlineStr"/>
+    </row>
+    <row r="343">
+      <c r="A343" s="3" t="inlineStr">
+        <is>
+          <t>TC-382</t>
+        </is>
+      </c>
+      <c r="B343" s="4" t="inlineStr">
+        <is>
+          <t>Map &amp; Geolocation</t>
+        </is>
+      </c>
+      <c r="C343" s="4" t="inlineStr">
+        <is>
+          <t>Clicking map pin shows donation detail popup</t>
+        </is>
+      </c>
+      <c r="D343" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E343" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F343" s="3" t="n">
+        <v>2346</v>
+      </c>
+      <c r="G343" s="4" t="inlineStr"/>
+    </row>
+    <row r="344">
+      <c r="A344" s="3" t="inlineStr">
+        <is>
+          <t>TC-383</t>
+        </is>
+      </c>
+      <c r="B344" s="4" t="inlineStr">
+        <is>
+          <t>Map &amp; Geolocation</t>
+        </is>
+      </c>
+      <c r="C344" s="4" t="inlineStr">
+        <is>
+          <t>Map zooms in on selected donation address</t>
+        </is>
+      </c>
+      <c r="D344" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E344" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F344" s="3" t="n">
+        <v>8428</v>
+      </c>
+      <c r="G344" s="4" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="3" t="inlineStr">
+        <is>
+          <t>TC-384</t>
+        </is>
+      </c>
+      <c r="B345" s="4" t="inlineStr">
+        <is>
+          <t>Map &amp; Geolocation</t>
+        </is>
+      </c>
+      <c r="C345" s="4" t="inlineStr">
+        <is>
+          <t>Geolocation permission prompt appears on first visit</t>
+        </is>
+      </c>
+      <c r="D345" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E345" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F345" s="3" t="n">
+        <v>8165</v>
+      </c>
+      <c r="G345" s="4" t="inlineStr"/>
+    </row>
+    <row r="346">
+      <c r="A346" s="3" t="inlineStr">
+        <is>
+          <t>TC-385</t>
+        </is>
+      </c>
+      <c r="B346" s="4" t="inlineStr">
+        <is>
+          <t>Map &amp; Geolocation</t>
+        </is>
+      </c>
+      <c r="C346" s="4" t="inlineStr">
+        <is>
+          <t>Fallback location used when geolocation denied</t>
+        </is>
+      </c>
+      <c r="D346" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E346" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F346" s="3" t="n">
+        <v>1569</v>
+      </c>
+      <c r="G346" s="4" t="inlineStr"/>
+    </row>
+    <row r="347">
+      <c r="A347" s="3" t="inlineStr">
+        <is>
+          <t>TC-386</t>
+        </is>
+      </c>
+      <c r="B347" s="4" t="inlineStr">
+        <is>
+          <t>Map &amp; Geolocation</t>
+        </is>
+      </c>
+      <c r="C347" s="4" t="inlineStr">
+        <is>
+          <t>Address auto-complete from coordinates works</t>
+        </is>
+      </c>
+      <c r="D347" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E347" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F347" s="3" t="n">
+        <v>12462</v>
+      </c>
+      <c r="G347" s="4" t="inlineStr"/>
+    </row>
+    <row r="348">
+      <c r="A348" s="3" t="inlineStr">
+        <is>
+          <t>TC-387</t>
+        </is>
+      </c>
+      <c r="B348" s="4" t="inlineStr">
+        <is>
+          <t>Map &amp; Geolocation</t>
+        </is>
+      </c>
+      <c r="C348" s="4" t="inlineStr">
+        <is>
+          <t>Donation lat/lng stored with 6 decimal precision</t>
+        </is>
+      </c>
+      <c r="D348" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E348" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F348" s="3" t="n">
+        <v>851</v>
+      </c>
+      <c r="G348" s="4" t="inlineStr"/>
+    </row>
+    <row r="349">
+      <c r="A349" s="3" t="inlineStr">
+        <is>
+          <t>TC-388</t>
+        </is>
+      </c>
+      <c r="B349" s="4" t="inlineStr">
+        <is>
+          <t>Map &amp; Geolocation</t>
+        </is>
+      </c>
+      <c r="C349" s="4" t="inlineStr">
+        <is>
+          <t>Distance radius filter shows nearby donations</t>
+        </is>
+      </c>
+      <c r="D349" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E349" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F349" s="3" t="n">
+        <v>14188</v>
+      </c>
+      <c r="G349" s="4" t="inlineStr"/>
+    </row>
+    <row r="350">
+      <c r="A350" s="3" t="inlineStr">
+        <is>
+          <t>TC-389</t>
+        </is>
+      </c>
+      <c r="B350" s="4" t="inlineStr">
+        <is>
+          <t>Map &amp; Geolocation</t>
+        </is>
+      </c>
+      <c r="C350" s="4" t="inlineStr">
+        <is>
+          <t>Multiple map layers toggle (satellite/street)</t>
+        </is>
+      </c>
+      <c r="D350" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E350" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F350" s="3" t="n">
+        <v>1876</v>
+      </c>
+      <c r="G350" s="4" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="3" t="inlineStr">
+        <is>
+          <t>TC-390</t>
+        </is>
+      </c>
+      <c r="B351" s="4" t="inlineStr">
+        <is>
+          <t>Map &amp; Geolocation</t>
+        </is>
+      </c>
+      <c r="C351" s="4" t="inlineStr">
+        <is>
+          <t>Map attribution links present and correct</t>
+        </is>
+      </c>
+      <c r="D351" s="3" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E351" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F351" s="3" t="n">
+        <v>2584</v>
+      </c>
+      <c r="G351" s="4" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="3" t="inlineStr">
+        <is>
+          <t>TC-391</t>
+        </is>
+      </c>
+      <c r="B352" s="4" t="inlineStr">
+        <is>
+          <t>Final Extended</t>
+        </is>
+      </c>
+      <c r="C352" s="4" t="inlineStr">
+        <is>
+          <t>API health endpoint /api/health returns 200</t>
+        </is>
+      </c>
+      <c r="D352" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E352" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F352" s="3" t="n">
+        <v>10360</v>
+      </c>
+      <c r="G352" s="4" t="inlineStr"/>
+    </row>
+    <row r="353">
+      <c r="A353" s="3" t="inlineStr">
+        <is>
+          <t>TC-392</t>
+        </is>
+      </c>
+      <c r="B353" s="4" t="inlineStr">
+        <is>
+          <t>Final Extended</t>
+        </is>
+      </c>
+      <c r="C353" s="4" t="inlineStr">
+        <is>
+          <t>API version endpoint /api/version returns string</t>
+        </is>
+      </c>
+      <c r="D353" s="3" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E353" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F353" s="3" t="n">
+        <v>2701</v>
+      </c>
+      <c r="G353" s="4" t="inlineStr"/>
+    </row>
+    <row r="354">
+      <c r="A354" s="3" t="inlineStr">
+        <is>
+          <t>TC-393</t>
+        </is>
+      </c>
+      <c r="B354" s="4" t="inlineStr">
+        <is>
+          <t>Final Extended</t>
+        </is>
+      </c>
+      <c r="C354" s="4" t="inlineStr">
+        <is>
+          <t>DB migration runs without error on fresh install</t>
+        </is>
+      </c>
+      <c r="D354" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E354" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F354" s="3" t="n">
+        <v>13057</v>
+      </c>
+      <c r="G354" s="4" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="3" t="inlineStr">
+        <is>
+          <t>TC-394</t>
+        </is>
+      </c>
+      <c r="B355" s="4" t="inlineStr">
+        <is>
+          <t>Final Extended</t>
+        </is>
+      </c>
+      <c r="C355" s="4" t="inlineStr">
+        <is>
+          <t>Environment variables loaded from .env correctly</t>
+        </is>
+      </c>
+      <c r="D355" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E355" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F355" s="3" t="n">
+        <v>11229</v>
+      </c>
+      <c r="G355" s="4" t="inlineStr"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="3" t="inlineStr">
+        <is>
+          <t>TC-395</t>
+        </is>
+      </c>
+      <c r="B356" s="4" t="inlineStr">
+        <is>
+          <t>Final Extended</t>
+        </is>
+      </c>
+      <c r="C356" s="4" t="inlineStr">
+        <is>
+          <t>Static assets served with correct Cache-Control</t>
+        </is>
+      </c>
+      <c r="D356" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E356" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F356" s="3" t="n">
+        <v>6996</v>
+      </c>
+      <c r="G356" s="4" t="inlineStr"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="3" t="inlineStr">
+        <is>
+          <t>TC-396</t>
+        </is>
+      </c>
+      <c r="B357" s="4" t="inlineStr">
+        <is>
+          <t>Final Extended</t>
+        </is>
+      </c>
+      <c r="C357" s="4" t="inlineStr">
+        <is>
+          <t>GZIP compression enabled for API responses</t>
+        </is>
+      </c>
+      <c r="D357" s="3" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E357" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F357" s="3" t="n">
+        <v>9851</v>
+      </c>
+      <c r="G357" s="4" t="inlineStr"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="3" t="inlineStr">
+        <is>
+          <t>TC-397</t>
+        </is>
+      </c>
+      <c r="B358" s="4" t="inlineStr">
+        <is>
+          <t>Final Extended</t>
+        </is>
+      </c>
+      <c r="C358" s="4" t="inlineStr">
+        <is>
+          <t>Error boundary catches React component crashes</t>
+        </is>
+      </c>
+      <c r="D358" s="3" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="E358" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F358" s="3" t="n">
+        <v>1120</v>
+      </c>
+      <c r="G358" s="4" t="inlineStr"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="3" t="inlineStr">
+        <is>
+          <t>TC-398</t>
+        </is>
+      </c>
+      <c r="B359" s="4" t="inlineStr">
+        <is>
+          <t>Final Extended</t>
+        </is>
+      </c>
+      <c r="C359" s="4" t="inlineStr">
+        <is>
+          <t>404 page shown for unknown routes</t>
+        </is>
+      </c>
+      <c r="D359" s="3" t="inlineStr">
+        <is>
+          <t>UI/UX</t>
+        </is>
+      </c>
+      <c r="E359" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F359" s="3" t="n">
+        <v>6384</v>
+      </c>
+      <c r="G359" s="4" t="inlineStr"/>
+    </row>
+    <row r="360">
+      <c r="A360" s="3" t="inlineStr">
+        <is>
+          <t>TC-399</t>
+        </is>
+      </c>
+      <c r="B360" s="4" t="inlineStr">
+        <is>
+          <t>Final Extended</t>
+        </is>
+      </c>
+      <c r="C360" s="4" t="inlineStr">
+        <is>
+          <t>App metadata (title, description) set correctly</t>
+        </is>
+      </c>
+      <c r="D360" s="3" t="inlineStr">
+        <is>
+          <t>Accessibility</t>
+        </is>
+      </c>
+      <c r="E360" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F360" s="3" t="n">
+        <v>6332</v>
+      </c>
+      <c r="G360" s="4" t="inlineStr"/>
+    </row>
+    <row r="361">
+      <c r="A361" s="3" t="inlineStr">
+        <is>
+          <t>TC-400</t>
+        </is>
+      </c>
+      <c r="B361" s="4" t="inlineStr">
+        <is>
+          <t>Final Extended</t>
+        </is>
+      </c>
+      <c r="C361" s="4" t="inlineStr">
+        <is>
+          <t>Full system smoke test — all services healthy</t>
+        </is>
+      </c>
+      <c r="D361" s="3" t="inlineStr">
+        <is>
+          <t>E2E</t>
+        </is>
+      </c>
+      <c r="E361" s="5" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="F361" s="3" t="n">
+        <v>9843</v>
+      </c>
+      <c r="G361" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -6365,68 +11646,68 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>Report Title</t>
         </is>
       </c>
-      <c r="B1" s="7" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Selenium Web Functional &amp; UI Test Report</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>2026-06-14 21:34:59</t>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-23 10:32:04</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Total Tests</t>
         </is>
       </c>
-      <c r="B3" s="7" t="n">
-        <v>188</v>
+      <c r="B3" s="8" t="n">
+        <v>358</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Passed</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
-        <v>188</v>
+      <c r="B4" s="8" t="n">
+        <v>357</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Failed</t>
         </is>
       </c>
-      <c r="B5" s="7" t="n">
-        <v>0</v>
+      <c r="B5" s="8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Pass Rate</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>100.00%</t>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>99.72%</t>
         </is>
       </c>
     </row>
